--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128580870</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128580868</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128580869</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128580870</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128580868</v>
       </c>
       <c r="B3" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128580869</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128580870</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128580868</v>
       </c>
       <c r="B3" t="n">
-        <v>82892</v>
+        <v>82897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128580870</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128580868</v>
       </c>
       <c r="B3" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,6 +977,3081 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129678425</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575513</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7012525</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129678429</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575438</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7012734</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129678442</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92034</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575422</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7012450</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129678421</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575412</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7012382</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129678818</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Erik-elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575350</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7012785</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129678438</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575264</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7012697</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129678444</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80175</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575305</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7012630</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129678420</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575423</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7012448</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129678426</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575467</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7012676</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129678445</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80175</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>575308</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7012562</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129678448</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80175</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>575261</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7012709</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129678416</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>575334</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7012592</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129678428</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>575416</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7012774</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129678422</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>575262</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7012542</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129678414</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>575411</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7012780</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129678431</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>575424</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7012521</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129678433</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>575295</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7012515</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129678415</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>575418</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7012773</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129678418</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>575428</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7012546</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129678443</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92034</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>575446</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7012349</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129678427</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>575435</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7012675</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129678435</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>575269</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7012673</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129678441</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92034</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>575432</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7012492</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129678417</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>575403</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7012602</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129678419</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>575431</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7012496</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129678440</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92034</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>575318</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7012643</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129678430</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>575453</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7012526</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129678434</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>575250</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7012580</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129678423</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91581</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>575229</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7012609</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129678446</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80175</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>575354</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7012563</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129678437</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>575201</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7012827</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1081,50 +1081,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678429</v>
+        <v>129678442</v>
       </c>
       <c r="B6" t="n">
-        <v>57730</v>
+        <v>92034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575438</v>
+        <v>575422</v>
       </c>
       <c r="R6" t="n">
-        <v>7012734</v>
+        <v>7012450</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1183,45 +1178,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678442</v>
+        <v>129678429</v>
       </c>
       <c r="B7" t="n">
-        <v>92034</v>
+        <v>57730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575422</v>
+        <v>575438</v>
       </c>
       <c r="R7" t="n">
-        <v>7012450</v>
+        <v>7012734</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678419</v>
+        <v>129678430</v>
       </c>
       <c r="B29" t="n">
-        <v>91581</v>
+        <v>57730</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3371,34 +3371,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575431</v>
+        <v>575453</v>
       </c>
       <c r="R29" t="n">
-        <v>7012496</v>
+        <v>7012526</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3457,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129678440</v>
+        <v>129678419</v>
       </c>
       <c r="B30" t="n">
-        <v>92034</v>
+        <v>91581</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3492,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575318</v>
+        <v>575431</v>
       </c>
       <c r="R30" t="n">
-        <v>7012643</v>
+        <v>7012496</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3554,50 +3559,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129678430</v>
+        <v>129678440</v>
       </c>
       <c r="B31" t="n">
-        <v>57730</v>
+        <v>92034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575453</v>
+        <v>575318</v>
       </c>
       <c r="R31" t="n">
-        <v>7012526</v>
+        <v>7012643</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,50 +979,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678425</v>
+        <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>92040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575513</v>
+        <v>575422</v>
       </c>
       <c r="R5" t="n">
-        <v>7012525</v>
+        <v>7012450</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1081,45 +1076,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678442</v>
+        <v>129678429</v>
       </c>
       <c r="B6" t="n">
-        <v>92034</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575422</v>
+        <v>575438</v>
       </c>
       <c r="R6" t="n">
-        <v>7012450</v>
+        <v>7012734</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678429</v>
+        <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,39 +1189,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575438</v>
+        <v>575412</v>
       </c>
       <c r="R7" t="n">
-        <v>7012734</v>
+        <v>7012382</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1280,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678421</v>
+        <v>129678818</v>
       </c>
       <c r="B8" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1291,37 +1286,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575412</v>
+        <v>575350</v>
       </c>
       <c r="R8" t="n">
-        <v>7012382</v>
+        <v>7012785</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678818</v>
+        <v>129678438</v>
       </c>
       <c r="B9" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1406,27 +1409,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Erik-elias bodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575350</v>
+        <v>575264</v>
       </c>
       <c r="R9" t="n">
-        <v>7012785</v>
+        <v>7012697</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B10" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,39 +1493,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R10" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1584,10 +1579,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129678444</v>
+        <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1595,21 +1590,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,10 +1614,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575305</v>
+        <v>575423</v>
       </c>
       <c r="R11" t="n">
-        <v>7012630</v>
+        <v>7012448</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1681,10 +1676,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129678420</v>
+        <v>129678426</v>
       </c>
       <c r="B12" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1687,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575423</v>
+        <v>575467</v>
       </c>
       <c r="R12" t="n">
-        <v>7012448</v>
+        <v>7012676</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678426</v>
+        <v>129678416</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,39 +1789,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575467</v>
+        <v>575334</v>
       </c>
       <c r="R13" t="n">
-        <v>7012676</v>
+        <v>7012592</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1883,7 +1878,7 @@
         <v>129678445</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1975,7 @@
         <v>129678448</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678416</v>
+        <v>129678428</v>
       </c>
       <c r="B16" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2085,34 +2080,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575334</v>
+        <v>575416</v>
       </c>
       <c r="R16" t="n">
-        <v>7012592</v>
+        <v>7012774</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678428</v>
+        <v>129678422</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2182,39 +2182,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575416</v>
+        <v>575262</v>
       </c>
       <c r="R17" t="n">
-        <v>7012774</v>
+        <v>7012542</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2273,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678422</v>
+        <v>129678414</v>
       </c>
       <c r="B18" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2308,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575262</v>
+        <v>575411</v>
       </c>
       <c r="R18" t="n">
-        <v>7012542</v>
+        <v>7012780</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2370,10 +2365,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129678414</v>
+        <v>129678431</v>
       </c>
       <c r="B19" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,34 +2376,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575411</v>
+        <v>575424</v>
       </c>
       <c r="R19" t="n">
-        <v>7012780</v>
+        <v>7012521</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129678431</v>
+        <v>129678433</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575424</v>
+        <v>575295</v>
       </c>
       <c r="R20" t="n">
-        <v>7012521</v>
+        <v>7012515</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678433</v>
+        <v>129678415</v>
       </c>
       <c r="B21" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2580,39 +2580,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575295</v>
+        <v>575418</v>
       </c>
       <c r="R21" t="n">
-        <v>7012515</v>
+        <v>7012773</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2671,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678415</v>
+        <v>129678418</v>
       </c>
       <c r="B22" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2706,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575418</v>
+        <v>575428</v>
       </c>
       <c r="R22" t="n">
-        <v>7012773</v>
+        <v>7012546</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2768,32 +2763,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129678418</v>
+        <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>91581</v>
+        <v>92040</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2803,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575428</v>
+        <v>575446</v>
       </c>
       <c r="R23" t="n">
-        <v>7012546</v>
+        <v>7012349</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2865,45 +2860,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129678443</v>
+        <v>129678435</v>
       </c>
       <c r="B24" t="n">
-        <v>92034</v>
+        <v>57735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575446</v>
+        <v>575269</v>
       </c>
       <c r="R24" t="n">
-        <v>7012349</v>
+        <v>7012673</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2962,50 +2962,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678427</v>
+        <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>57730</v>
+        <v>92040</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575435</v>
+        <v>575432</v>
       </c>
       <c r="R25" t="n">
-        <v>7012675</v>
+        <v>7012492</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3064,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678435</v>
+        <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>91587</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3075,39 +3070,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575269</v>
+        <v>575403</v>
       </c>
       <c r="R26" t="n">
-        <v>7012673</v>
+        <v>7012602</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3166,45 +3156,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678441</v>
+        <v>129678430</v>
       </c>
       <c r="B27" t="n">
-        <v>92034</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575432</v>
+        <v>575453</v>
       </c>
       <c r="R27" t="n">
-        <v>7012492</v>
+        <v>7012526</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3263,10 +3258,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678417</v>
+        <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3298,10 +3293,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575403</v>
+        <v>575431</v>
       </c>
       <c r="R28" t="n">
-        <v>7012602</v>
+        <v>7012496</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3360,50 +3355,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678430</v>
+        <v>129678440</v>
       </c>
       <c r="B29" t="n">
-        <v>57730</v>
+        <v>92040</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575453</v>
+        <v>575318</v>
       </c>
       <c r="R29" t="n">
-        <v>7012526</v>
+        <v>7012643</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3462,10 +3452,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129678419</v>
+        <v>129678434</v>
       </c>
       <c r="B30" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3473,34 +3463,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575431</v>
+        <v>575250</v>
       </c>
       <c r="R30" t="n">
-        <v>7012496</v>
+        <v>7012580</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3559,32 +3554,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129678440</v>
+        <v>129678423</v>
       </c>
       <c r="B31" t="n">
-        <v>92034</v>
+        <v>91587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3594,10 +3589,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575318</v>
+        <v>575229</v>
       </c>
       <c r="R31" t="n">
-        <v>7012643</v>
+        <v>7012609</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3656,10 +3651,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129678434</v>
+        <v>129678446</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3667,39 +3662,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575250</v>
+        <v>575354</v>
       </c>
       <c r="R32" t="n">
-        <v>7012580</v>
+        <v>7012563</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3758,10 +3748,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129678423</v>
+        <v>129678437</v>
       </c>
       <c r="B33" t="n">
-        <v>91581</v>
+        <v>57735</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3769,34 +3759,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575229</v>
+        <v>575201</v>
       </c>
       <c r="R33" t="n">
-        <v>7012609</v>
+        <v>7012827</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3855,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129678446</v>
+        <v>129701251</v>
       </c>
       <c r="B34" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3866,37 +3861,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575354</v>
+        <v>575332</v>
       </c>
       <c r="R34" t="n">
-        <v>7012563</v>
+        <v>7012509</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,12 +3915,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3940,22 +3935,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129678437</v>
+        <v>129701172</v>
       </c>
       <c r="B35" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3983,22 +3978,22 @@
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575201</v>
+        <v>575342</v>
       </c>
       <c r="R35" t="n">
-        <v>7012827</v>
+        <v>7012553</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4022,12 +4017,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4042,15 +4042,3966 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129678425</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>575513</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7012525</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>Dennis Pålsson</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>Dennis Pålsson</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129702616</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92006</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>575529</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7012502</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129700543</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97639</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>575483</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7012735</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129712552</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>575303</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7012573</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129701118</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>575354</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7012577</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129712548</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>575383</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7012472</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129702590</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91607</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>575529</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7012502</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129702652</v>
+      </c>
+      <c r="B43" t="n">
+        <v>83027</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>575531</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7012502</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129700674</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>575458</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7012679</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129702459</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>575495</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7012552</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129701504</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>575431</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7012562</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129702105</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>575427</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7012592</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129700728</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>575445</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7012641</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129702707</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>575543</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7012496</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129700982</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>575401</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7012650</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129700719</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>575458</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7012663</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129712549</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>575210</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7012839</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129712558</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>575222</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7012818</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129701024</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>575367</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7012641</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129701902</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>575412</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7012629</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129701129</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80209</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>575358</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7012565</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129702749</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>575545</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7012515</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129700911</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92305</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>575418</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7012634</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129712554</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>575257</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7012718</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129712553</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>575515</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7012371</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129700955</v>
+      </c>
+      <c r="B61" t="n">
+        <v>83036</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>308</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>575420</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7012646</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129701829</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>575378</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7012599</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129700923</v>
+      </c>
+      <c r="B63" t="n">
+        <v>82910</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>575418</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7012634</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129678427</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>575435</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7012675</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129702542</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80216</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>575538</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7012552</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129702401</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>575471</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7012565</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129701965</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>575412</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7012614</v>
+      </c>
+      <c r="S67" t="n">
+        <v>15</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129702002</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>575427</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7012593</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129702771</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92305</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>575545</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7012515</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129702290</v>
+      </c>
+      <c r="B70" t="n">
+        <v>83027</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>575476</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7012589</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129702355</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>575474</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7012588</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129712551</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80180</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>575310</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7012647</v>
+      </c>
+      <c r="S72" t="n">
+        <v>20</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129700952</v>
+      </c>
+      <c r="B73" t="n">
+        <v>83044</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>575428</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7012641</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129701072</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>575348</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7012619</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129702579</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>575529</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7012502</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>129678429</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>129678818</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,39 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R9" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1482,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B10" t="n">
-        <v>80180</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,34 +1488,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R10" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129678426</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678416</v>
+        <v>129678448</v>
       </c>
       <c r="B13" t="n">
-        <v>91587</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575334</v>
+        <v>575261</v>
       </c>
       <c r="R13" t="n">
-        <v>7012592</v>
+        <v>7012709</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129678445</v>
+        <v>129678416</v>
       </c>
       <c r="B14" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575308</v>
+        <v>575334</v>
       </c>
       <c r="R14" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129678448</v>
+        <v>129678445</v>
       </c>
       <c r="B15" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575261</v>
+        <v>575308</v>
       </c>
       <c r="R15" t="n">
-        <v>7012709</v>
+        <v>7012562</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678428</v>
+        <v>129678422</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,39 +2080,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575416</v>
+        <v>575262</v>
       </c>
       <c r="R16" t="n">
-        <v>7012774</v>
+        <v>7012542</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2171,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678422</v>
+        <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575262</v>
+        <v>575411</v>
       </c>
       <c r="R17" t="n">
-        <v>7012542</v>
+        <v>7012780</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678414</v>
+        <v>129678428</v>
       </c>
       <c r="B18" t="n">
-        <v>91587</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,34 +2274,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575411</v>
+        <v>575416</v>
       </c>
       <c r="R18" t="n">
-        <v>7012780</v>
+        <v>7012774</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2368,7 +2368,7 @@
         <v>129678431</v>
       </c>
       <c r="B19" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>129678433</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129678415</v>
       </c>
       <c r="B21" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129678418</v>
       </c>
       <c r="B22" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>129678435</v>
       </c>
       <c r="B24" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>129678430</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>129678440</v>
       </c>
       <c r="B29" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129678434</v>
+        <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3463,39 +3463,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575250</v>
+        <v>575229</v>
       </c>
       <c r="R30" t="n">
-        <v>7012580</v>
+        <v>7012609</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3554,10 +3549,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129678423</v>
+        <v>129678434</v>
       </c>
       <c r="B31" t="n">
-        <v>91587</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3565,34 +3560,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575229</v>
+        <v>575250</v>
       </c>
       <c r="R31" t="n">
-        <v>7012609</v>
+        <v>7012580</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3654,7 +3654,7 @@
         <v>129678446</v>
       </c>
       <c r="B32" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129678437</v>
       </c>
       <c r="B33" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701251</v>
+        <v>129702616</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>92007</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,34 +3861,29 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575332</v>
+        <v>575529</v>
       </c>
       <c r="R34" t="n">
-        <v>7012509</v>
+        <v>7012502</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3947,10 +3942,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129701172</v>
+        <v>129678425</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3983,17 +3978,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575342</v>
+        <v>575513</v>
       </c>
       <c r="R35" t="n">
-        <v>7012553</v>
+        <v>7012525</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4017,17 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4042,22 +4032,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129678425</v>
+        <v>129701172</v>
       </c>
       <c r="B36" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4090,17 +4080,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575513</v>
+        <v>575342</v>
       </c>
       <c r="R36" t="n">
-        <v>7012525</v>
+        <v>7012553</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4124,12 +4114,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,52 +4139,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129702616</v>
+        <v>129700543</v>
       </c>
       <c r="B37" t="n">
-        <v>92006</v>
+        <v>97640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575529</v>
+        <v>575483</v>
       </c>
       <c r="R37" t="n">
-        <v>7012502</v>
+        <v>7012735</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4248,32 +4248,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129700543</v>
+        <v>129701251</v>
       </c>
       <c r="B38" t="n">
-        <v>97639</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575483</v>
+        <v>575332</v>
       </c>
       <c r="R38" t="n">
-        <v>7012735</v>
+        <v>7012509</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4348,7 +4348,7 @@
         <v>129712552</v>
       </c>
       <c r="B39" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>129701118</v>
       </c>
       <c r="B40" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129712548</v>
+        <v>129702590</v>
       </c>
       <c r="B41" t="n">
-        <v>57735</v>
+        <v>91608</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4550,42 +4550,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575383</v>
+        <v>575529</v>
       </c>
       <c r="R41" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4609,12 +4600,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4629,22 +4620,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702590</v>
+        <v>129712548</v>
       </c>
       <c r="B42" t="n">
-        <v>91607</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4652,33 +4643,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575529</v>
+        <v>575383</v>
       </c>
       <c r="R42" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4702,12 +4702,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4722,12 +4722,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4737,7 +4737,7 @@
         <v>129702652</v>
       </c>
       <c r="B43" t="n">
-        <v>83027</v>
+        <v>83028</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4831,10 +4831,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129700674</v>
+        <v>129702459</v>
       </c>
       <c r="B44" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,34 +4842,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575458</v>
+        <v>575495</v>
       </c>
       <c r="R44" t="n">
-        <v>7012679</v>
+        <v>7012552</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4902,6 +4907,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4928,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129702459</v>
+        <v>129700674</v>
       </c>
       <c r="B45" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,39 +4949,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575495</v>
+        <v>575458</v>
       </c>
       <c r="R45" t="n">
-        <v>7012552</v>
+        <v>7012679</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5004,11 +5009,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5038,7 +5038,7 @@
         <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>129702105</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>129700728</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129702707</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>129700719</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>129712549</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5750,37 +5750,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R53" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5824,22 +5824,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B54" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R54" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5936,7 +5936,7 @@
         <v>129701902</v>
       </c>
       <c r="B55" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B56" t="n">
-        <v>80209</v>
+        <v>92306</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6051,21 +6051,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R56" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6140,7 +6140,7 @@
         <v>129702749</v>
       </c>
       <c r="B57" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B58" t="n">
-        <v>92305</v>
+        <v>80210</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R58" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129712554</v>
+        <v>129700955</v>
       </c>
       <c r="B59" t="n">
-        <v>80180</v>
+        <v>83037</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6352,37 +6352,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575257</v>
+        <v>575420</v>
       </c>
       <c r="R59" t="n">
-        <v>7012718</v>
+        <v>7012646</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6406,12 +6406,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6426,22 +6426,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129712553</v>
+        <v>129701829</v>
       </c>
       <c r="B60" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,37 +6449,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575515</v>
+        <v>575378</v>
       </c>
       <c r="R60" t="n">
-        <v>7012371</v>
+        <v>7012599</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6503,12 +6503,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6523,22 +6523,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129700955</v>
+        <v>129678427</v>
       </c>
       <c r="B61" t="n">
-        <v>83036</v>
+        <v>57736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6546,37 +6546,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575420</v>
+        <v>575435</v>
       </c>
       <c r="R61" t="n">
-        <v>7012646</v>
+        <v>7012675</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6600,12 +6605,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6620,22 +6625,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129701829</v>
+        <v>129700923</v>
       </c>
       <c r="B62" t="n">
-        <v>91587</v>
+        <v>82911</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6643,21 +6648,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6667,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R62" t="n">
-        <v>7012599</v>
+        <v>7012634</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6729,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129700923</v>
+        <v>129712554</v>
       </c>
       <c r="B63" t="n">
-        <v>82910</v>
+        <v>80181</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6740,37 +6745,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575418</v>
+        <v>575257</v>
       </c>
       <c r="R63" t="n">
-        <v>7012634</v>
+        <v>7012718</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6794,12 +6799,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6814,22 +6819,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129678427</v>
+        <v>129712553</v>
       </c>
       <c r="B64" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6837,39 +6842,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575435</v>
+        <v>575515</v>
       </c>
       <c r="R64" t="n">
-        <v>7012675</v>
+        <v>7012371</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6931,7 +6931,7 @@
         <v>129702542</v>
       </c>
       <c r="B65" t="n">
-        <v>80216</v>
+        <v>80217</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>129702401</v>
       </c>
       <c r="B66" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>129701965</v>
       </c>
       <c r="B67" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7219,50 +7219,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702002</v>
+        <v>129702771</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>92306</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575427</v>
+        <v>575545</v>
       </c>
       <c r="R68" t="n">
-        <v>7012593</v>
+        <v>7012515</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7295,11 +7290,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7326,45 +7316,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702771</v>
+        <v>129702002</v>
       </c>
       <c r="B69" t="n">
-        <v>92305</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575545</v>
+        <v>575427</v>
       </c>
       <c r="R69" t="n">
-        <v>7012515</v>
+        <v>7012593</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7397,6 +7392,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7426,7 +7426,7 @@
         <v>129702290</v>
       </c>
       <c r="B70" t="n">
-        <v>83027</v>
+        <v>83028</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>129712551</v>
       </c>
       <c r="B72" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>129700952</v>
       </c>
       <c r="B73" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B74" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7822,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R74" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B75" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,34 +7919,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R75" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678448</v>
+        <v>129678416</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>91588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575261</v>
+        <v>575334</v>
       </c>
       <c r="R13" t="n">
-        <v>7012709</v>
+        <v>7012592</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129678416</v>
+        <v>129678445</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575334</v>
+        <v>575308</v>
       </c>
       <c r="R14" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,7 +1972,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129678445</v>
+        <v>129678448</v>
       </c>
       <c r="B15" t="n">
         <v>80181</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575308</v>
+        <v>575261</v>
       </c>
       <c r="R15" t="n">
-        <v>7012562</v>
+        <v>7012709</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678422</v>
+        <v>129678428</v>
       </c>
       <c r="B16" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,34 +2080,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575262</v>
+        <v>575416</v>
       </c>
       <c r="R16" t="n">
-        <v>7012542</v>
+        <v>7012774</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2263,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678428</v>
+        <v>129678422</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>91588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,39 +2279,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575416</v>
+        <v>575262</v>
       </c>
       <c r="R18" t="n">
-        <v>7012774</v>
+        <v>7012542</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -6040,45 +6040,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129700911</v>
+        <v>129702749</v>
       </c>
       <c r="B56" t="n">
-        <v>92306</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575418</v>
+        <v>575545</v>
       </c>
       <c r="R56" t="n">
-        <v>7012634</v>
+        <v>7012515</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6111,6 +6116,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6137,50 +6147,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129702749</v>
+        <v>129701129</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>80210</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575545</v>
+        <v>575358</v>
       </c>
       <c r="R57" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6213,11 +6218,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6244,10 +6244,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B58" t="n">
-        <v>80210</v>
+        <v>92306</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702401</v>
+        <v>129701965</v>
       </c>
       <c r="B66" t="n">
-        <v>79076</v>
+        <v>91584</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575471</v>
+        <v>575412</v>
       </c>
       <c r="R66" t="n">
-        <v>7012565</v>
+        <v>7012614</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129701965</v>
+        <v>129702002</v>
       </c>
       <c r="B67" t="n">
-        <v>91584</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7133,34 +7133,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575412</v>
+        <v>575427</v>
       </c>
       <c r="R67" t="n">
-        <v>7012614</v>
+        <v>7012593</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7193,6 +7198,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7316,10 +7326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702002</v>
+        <v>129702401</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79076</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7327,39 +7337,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575427</v>
+        <v>575471</v>
       </c>
       <c r="R69" t="n">
-        <v>7012593</v>
+        <v>7012565</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7392,11 +7397,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>129678416</v>
       </c>
       <c r="B13" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129678445</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>129678448</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678428</v>
+        <v>129678422</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,39 +2080,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575416</v>
+        <v>575262</v>
       </c>
       <c r="R16" t="n">
-        <v>7012774</v>
+        <v>7012542</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2174,7 +2169,7 @@
         <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678422</v>
+        <v>129678428</v>
       </c>
       <c r="B18" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,34 +2274,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575262</v>
+        <v>575416</v>
       </c>
       <c r="R18" t="n">
-        <v>7012542</v>
+        <v>7012774</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678415</v>
+        <v>129678418</v>
       </c>
       <c r="B21" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575418</v>
+        <v>575428</v>
       </c>
       <c r="R21" t="n">
-        <v>7012773</v>
+        <v>7012546</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678418</v>
+        <v>129678415</v>
       </c>
       <c r="B22" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575428</v>
+        <v>575418</v>
       </c>
       <c r="R22" t="n">
-        <v>7012546</v>
+        <v>7012773</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2766,7 +2766,7 @@
         <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>129678440</v>
       </c>
       <c r="B29" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129678446</v>
       </c>
       <c r="B32" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129702616</v>
+        <v>129701251</v>
       </c>
       <c r="B34" t="n">
-        <v>92007</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,29 +3861,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575529</v>
+        <v>575332</v>
       </c>
       <c r="R34" t="n">
-        <v>7012502</v>
+        <v>7012509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4154,7 +4159,7 @@
         <v>129700543</v>
       </c>
       <c r="B37" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4248,10 +4253,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129701251</v>
+        <v>129702616</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>92012</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4259,34 +4264,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575332</v>
+        <v>575529</v>
       </c>
       <c r="R38" t="n">
-        <v>7012509</v>
+        <v>7012502</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4348,7 +4348,7 @@
         <v>129712552</v>
       </c>
       <c r="B39" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>129701118</v>
       </c>
       <c r="B40" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>129702590</v>
       </c>
       <c r="B41" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4632,53 +4632,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129712548</v>
+        <v>129702652</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>83033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575383</v>
+        <v>575531</v>
       </c>
       <c r="R42" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4702,12 +4697,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4722,60 +4717,65 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129702652</v>
+        <v>129712548</v>
       </c>
       <c r="B43" t="n">
-        <v>83028</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575531</v>
+        <v>575383</v>
       </c>
       <c r="R43" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4819,12 +4819,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4941,7 +4941,7 @@
         <v>129700674</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>129700728</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>129702707</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>129701024</v>
       </c>
       <c r="B53" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129712558</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B57" t="n">
-        <v>80210</v>
+        <v>92311</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B58" t="n">
-        <v>92306</v>
+        <v>80215</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R58" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6344,7 +6344,7 @@
         <v>129700955</v>
       </c>
       <c r="B59" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>129701829</v>
       </c>
       <c r="B60" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129678427</v>
+        <v>129700923</v>
       </c>
       <c r="B61" t="n">
-        <v>57736</v>
+        <v>82916</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6546,42 +6546,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575435</v>
+        <v>575418</v>
       </c>
       <c r="R61" t="n">
-        <v>7012675</v>
+        <v>7012634</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6605,12 +6600,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6625,22 +6620,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129700923</v>
+        <v>129678427</v>
       </c>
       <c r="B62" t="n">
-        <v>82911</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,37 +6643,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575418</v>
+        <v>575435</v>
       </c>
       <c r="R62" t="n">
-        <v>7012634</v>
+        <v>7012675</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6722,12 +6722,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6737,7 +6737,7 @@
         <v>129712554</v>
       </c>
       <c r="B63" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>129712553</v>
       </c>
       <c r="B64" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>129702542</v>
       </c>
       <c r="B65" t="n">
-        <v>80217</v>
+        <v>80222</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,45 +7025,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129701965</v>
+        <v>129702771</v>
       </c>
       <c r="B66" t="n">
-        <v>91584</v>
+        <v>92311</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575412</v>
+        <v>575545</v>
       </c>
       <c r="R66" t="n">
-        <v>7012614</v>
+        <v>7012515</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702002</v>
+        <v>129701965</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7133,39 +7133,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575427</v>
+        <v>575412</v>
       </c>
       <c r="R67" t="n">
-        <v>7012593</v>
+        <v>7012614</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7198,11 +7193,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7229,45 +7219,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702771</v>
+        <v>129702401</v>
       </c>
       <c r="B68" t="n">
-        <v>92306</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575545</v>
+        <v>575471</v>
       </c>
       <c r="R68" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7326,10 +7316,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702401</v>
+        <v>129702002</v>
       </c>
       <c r="B69" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7337,34 +7327,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575471</v>
+        <v>575427</v>
       </c>
       <c r="R69" t="n">
-        <v>7012565</v>
+        <v>7012593</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7397,6 +7392,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7426,7 +7426,7 @@
         <v>129702290</v>
       </c>
       <c r="B70" t="n">
-        <v>83028</v>
+        <v>83033</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>129712551</v>
       </c>
       <c r="B72" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>129700952</v>
       </c>
       <c r="B73" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>129702579</v>
       </c>
       <c r="B74" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>129701072</v>
       </c>
       <c r="B75" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678416</v>
+        <v>129678445</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575334</v>
+        <v>575308</v>
       </c>
       <c r="R13" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129678445</v>
+        <v>129678448</v>
       </c>
       <c r="B14" t="n">
         <v>80186</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575308</v>
+        <v>575261</v>
       </c>
       <c r="R14" t="n">
-        <v>7012562</v>
+        <v>7012709</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129678448</v>
+        <v>129678416</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575261</v>
+        <v>575334</v>
       </c>
       <c r="R15" t="n">
-        <v>7012709</v>
+        <v>7012592</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678422</v>
+        <v>129678414</v>
       </c>
       <c r="B16" t="n">
         <v>91593</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575262</v>
+        <v>575411</v>
       </c>
       <c r="R16" t="n">
-        <v>7012542</v>
+        <v>7012780</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678414</v>
+        <v>129678428</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,34 +2177,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575411</v>
+        <v>575416</v>
       </c>
       <c r="R17" t="n">
-        <v>7012780</v>
+        <v>7012774</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2263,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678428</v>
+        <v>129678422</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,39 +2279,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575416</v>
+        <v>575262</v>
       </c>
       <c r="R18" t="n">
-        <v>7012774</v>
+        <v>7012542</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678418</v>
+        <v>129678415</v>
       </c>
       <c r="B21" t="n">
         <v>91593</v>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575428</v>
+        <v>575418</v>
       </c>
       <c r="R21" t="n">
-        <v>7012546</v>
+        <v>7012773</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678415</v>
+        <v>129678418</v>
       </c>
       <c r="B22" t="n">
         <v>91593</v>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575418</v>
+        <v>575428</v>
       </c>
       <c r="R22" t="n">
-        <v>7012773</v>
+        <v>7012546</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -3156,50 +3156,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678430</v>
+        <v>129678440</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>92046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575453</v>
+        <v>575318</v>
       </c>
       <c r="R27" t="n">
-        <v>7012526</v>
+        <v>7012643</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3355,45 +3350,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678440</v>
+        <v>129678430</v>
       </c>
       <c r="B29" t="n">
-        <v>92046</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575318</v>
+        <v>575453</v>
       </c>
       <c r="R29" t="n">
-        <v>7012643</v>
+        <v>7012526</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129678425</v>
+        <v>129701172</v>
       </c>
       <c r="B35" t="n">
         <v>57736</v>
@@ -3983,17 +3983,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575513</v>
+        <v>575342</v>
       </c>
       <c r="R35" t="n">
-        <v>7012525</v>
+        <v>7012553</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4017,12 +4017,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4037,22 +4042,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129701172</v>
+        <v>129702616</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>92012</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4060,39 +4065,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575342</v>
+        <v>575529</v>
       </c>
       <c r="R36" t="n">
-        <v>7012553</v>
+        <v>7012502</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4125,11 +4120,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4253,10 +4243,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129702616</v>
+        <v>129678425</v>
       </c>
       <c r="B38" t="n">
-        <v>92012</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4264,32 +4254,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575529</v>
+        <v>575513</v>
       </c>
       <c r="R38" t="n">
-        <v>7012502</v>
+        <v>7012525</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4333,12 +4333,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4539,30 +4539,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702590</v>
+        <v>129702652</v>
       </c>
       <c r="B41" t="n">
-        <v>91613</v>
+        <v>83033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4570,7 +4574,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575529</v>
+        <v>575531</v>
       </c>
       <c r="R41" t="n">
         <v>7012502</v>
@@ -4632,48 +4636,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702652</v>
+        <v>129712548</v>
       </c>
       <c r="B42" t="n">
-        <v>83033</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575531</v>
+        <v>575383</v>
       </c>
       <c r="R42" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4697,12 +4706,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4717,22 +4726,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129712548</v>
+        <v>129702590</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4740,42 +4749,33 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575383</v>
+        <v>575529</v>
       </c>
       <c r="R43" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4819,12 +4819,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,34 +5046,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R46" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5106,6 +5111,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5132,10 +5142,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,39 +5153,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R47" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5208,11 +5213,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B57" t="n">
-        <v>92311</v>
+        <v>80215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R57" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B58" t="n">
-        <v>80215</v>
+        <v>92311</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700955</v>
+        <v>129678427</v>
       </c>
       <c r="B59" t="n">
-        <v>83042</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6352,37 +6352,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575420</v>
+        <v>575435</v>
       </c>
       <c r="R59" t="n">
-        <v>7012646</v>
+        <v>7012675</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6406,12 +6411,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6426,22 +6431,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129701829</v>
+        <v>129700955</v>
       </c>
       <c r="B60" t="n">
-        <v>91593</v>
+        <v>83042</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575378</v>
+        <v>575420</v>
       </c>
       <c r="R60" t="n">
-        <v>7012599</v>
+        <v>7012646</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6535,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129700923</v>
+        <v>129712554</v>
       </c>
       <c r="B61" t="n">
-        <v>82916</v>
+        <v>80186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6546,37 +6551,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575418</v>
+        <v>575257</v>
       </c>
       <c r="R61" t="n">
-        <v>7012634</v>
+        <v>7012718</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6600,12 +6605,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6620,22 +6625,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129678427</v>
+        <v>129712553</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6643,39 +6648,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575435</v>
+        <v>575515</v>
       </c>
       <c r="R62" t="n">
-        <v>7012675</v>
+        <v>7012371</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129712554</v>
+        <v>129701829</v>
       </c>
       <c r="B63" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,37 +6745,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575257</v>
+        <v>575378</v>
       </c>
       <c r="R63" t="n">
-        <v>7012718</v>
+        <v>7012599</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6819,22 +6819,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129712553</v>
+        <v>129700923</v>
       </c>
       <c r="B64" t="n">
-        <v>80186</v>
+        <v>82916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,37 +6842,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575515</v>
+        <v>575418</v>
       </c>
       <c r="R64" t="n">
-        <v>7012371</v>
+        <v>7012634</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6916,12 +6916,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7025,45 +7025,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702771</v>
+        <v>129701965</v>
       </c>
       <c r="B66" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575545</v>
+        <v>575412</v>
       </c>
       <c r="R66" t="n">
-        <v>7012515</v>
+        <v>7012614</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7122,10 +7122,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129701965</v>
+        <v>129702401</v>
       </c>
       <c r="B67" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7133,21 +7133,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575412</v>
+        <v>575471</v>
       </c>
       <c r="R67" t="n">
-        <v>7012614</v>
+        <v>7012565</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7219,45 +7219,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702401</v>
+        <v>129702771</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>92311</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575471</v>
+        <v>575545</v>
       </c>
       <c r="R68" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B74" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7822,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R74" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,34 +7919,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R75" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1391,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R9" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1477,10 +1482,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,39 +1493,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R10" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678414</v>
+        <v>129678422</v>
       </c>
       <c r="B16" t="n">
         <v>91593</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575411</v>
+        <v>575262</v>
       </c>
       <c r="R16" t="n">
-        <v>7012780</v>
+        <v>7012542</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678428</v>
+        <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,39 +2177,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575416</v>
+        <v>575411</v>
       </c>
       <c r="R17" t="n">
-        <v>7012774</v>
+        <v>7012780</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678422</v>
+        <v>129678428</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,34 +2274,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575262</v>
+        <v>575416</v>
       </c>
       <c r="R18" t="n">
-        <v>7012542</v>
+        <v>7012774</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -3156,32 +3156,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678440</v>
+        <v>129678419</v>
       </c>
       <c r="B27" t="n">
-        <v>92046</v>
+        <v>91593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575318</v>
+        <v>575431</v>
       </c>
       <c r="R27" t="n">
-        <v>7012643</v>
+        <v>7012496</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3253,32 +3253,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678419</v>
+        <v>129678440</v>
       </c>
       <c r="B28" t="n">
-        <v>91593</v>
+        <v>92046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575431</v>
+        <v>575318</v>
       </c>
       <c r="R28" t="n">
-        <v>7012496</v>
+        <v>7012643</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3850,32 +3850,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701251</v>
+        <v>129700543</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>97645</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575332</v>
+        <v>575483</v>
       </c>
       <c r="R34" t="n">
-        <v>7012509</v>
+        <v>7012735</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129701172</v>
+        <v>129702616</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>92012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,39 +3958,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575342</v>
+        <v>575529</v>
       </c>
       <c r="R35" t="n">
-        <v>7012553</v>
+        <v>7012502</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4023,11 +4013,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4054,10 +4039,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129702616</v>
+        <v>129701251</v>
       </c>
       <c r="B36" t="n">
-        <v>92012</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4065,29 +4050,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575529</v>
+        <v>575332</v>
       </c>
       <c r="R36" t="n">
-        <v>7012502</v>
+        <v>7012509</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4146,48 +4136,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129700543</v>
+        <v>129678425</v>
       </c>
       <c r="B37" t="n">
-        <v>97645</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575483</v>
+        <v>575513</v>
       </c>
       <c r="R37" t="n">
-        <v>7012735</v>
+        <v>7012525</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4211,12 +4206,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4231,19 +4226,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129678425</v>
+        <v>129701172</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -4279,17 +4274,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575513</v>
+        <v>575342</v>
       </c>
       <c r="R38" t="n">
-        <v>7012525</v>
+        <v>7012553</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4313,12 +4308,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4333,60 +4333,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129712552</v>
+        <v>129701118</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>91557</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575303</v>
+        <v>575354</v>
       </c>
       <c r="R39" t="n">
-        <v>7012573</v>
+        <v>7012577</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4430,60 +4430,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129701118</v>
+        <v>129712552</v>
       </c>
       <c r="B40" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575354</v>
+        <v>575303</v>
       </c>
       <c r="R40" t="n">
-        <v>7012577</v>
+        <v>7012573</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4527,46 +4527,42 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702652</v>
+        <v>129702590</v>
       </c>
       <c r="B41" t="n">
-        <v>83033</v>
+        <v>91613</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4574,7 +4570,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575531</v>
+        <v>575529</v>
       </c>
       <c r="R41" t="n">
         <v>7012502</v>
@@ -4636,53 +4632,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129712548</v>
+        <v>129702652</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>83033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575383</v>
+        <v>575531</v>
       </c>
       <c r="R42" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4706,12 +4697,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4726,22 +4717,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129702590</v>
+        <v>129712548</v>
       </c>
       <c r="B43" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4749,33 +4740,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575529</v>
+        <v>575383</v>
       </c>
       <c r="R43" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4819,22 +4819,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129702459</v>
+        <v>129700674</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,39 +4842,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575495</v>
+        <v>575458</v>
       </c>
       <c r="R44" t="n">
-        <v>7012552</v>
+        <v>7012679</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4907,11 +4902,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4938,10 +4928,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129700674</v>
+        <v>129702459</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4949,34 +4939,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575458</v>
+        <v>575495</v>
       </c>
       <c r="R45" t="n">
-        <v>7012679</v>
+        <v>7012552</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5009,6 +5004,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B53" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5750,37 +5750,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R53" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5824,22 +5824,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R54" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B57" t="n">
-        <v>80215</v>
+        <v>92311</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6158,21 +6158,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6244,10 +6244,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B58" t="n">
-        <v>92311</v>
+        <v>80215</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6255,21 +6255,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R58" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6341,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129678427</v>
+        <v>129700955</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>83042</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6352,42 +6352,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575435</v>
+        <v>575420</v>
       </c>
       <c r="R59" t="n">
-        <v>7012675</v>
+        <v>7012646</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6411,12 +6406,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6431,22 +6426,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129700955</v>
+        <v>129712553</v>
       </c>
       <c r="B60" t="n">
-        <v>83042</v>
+        <v>80186</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,37 +6449,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575420</v>
+        <v>575515</v>
       </c>
       <c r="R60" t="n">
-        <v>7012646</v>
+        <v>7012371</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6508,12 +6503,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6528,12 +6523,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6637,10 +6632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129712553</v>
+        <v>129701829</v>
       </c>
       <c r="B62" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,37 +6643,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575515</v>
+        <v>575378</v>
       </c>
       <c r="R62" t="n">
-        <v>7012371</v>
+        <v>7012599</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6702,12 +6697,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6722,22 +6717,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129701829</v>
+        <v>129700923</v>
       </c>
       <c r="B63" t="n">
-        <v>91593</v>
+        <v>82916</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,21 +6740,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6769,10 +6764,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R63" t="n">
-        <v>7012599</v>
+        <v>7012634</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6831,10 +6826,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129700923</v>
+        <v>129678427</v>
       </c>
       <c r="B64" t="n">
-        <v>82916</v>
+        <v>57736</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,37 +6837,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575418</v>
+        <v>575435</v>
       </c>
       <c r="R64" t="n">
-        <v>7012634</v>
+        <v>7012675</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6916,12 +6916,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7025,45 +7025,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129701965</v>
+        <v>129702771</v>
       </c>
       <c r="B66" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575412</v>
+        <v>575545</v>
       </c>
       <c r="R66" t="n">
-        <v>7012614</v>
+        <v>7012515</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7219,45 +7219,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702771</v>
+        <v>129702002</v>
       </c>
       <c r="B68" t="n">
-        <v>92311</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575545</v>
+        <v>575427</v>
       </c>
       <c r="R68" t="n">
-        <v>7012515</v>
+        <v>7012593</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7290,6 +7295,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7316,10 +7326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702002</v>
+        <v>129701965</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7327,39 +7337,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575427</v>
+        <v>575412</v>
       </c>
       <c r="R69" t="n">
-        <v>7012593</v>
+        <v>7012614</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7392,11 +7397,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7822,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R74" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B75" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,34 +7919,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R75" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678421</v>
+        <v>129678818</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,37 +1189,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575412</v>
+        <v>575350</v>
       </c>
       <c r="R7" t="n">
-        <v>7012382</v>
+        <v>7012785</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678818</v>
+        <v>129678421</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,45 +1294,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Erik-elias bodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575350</v>
+        <v>575412</v>
       </c>
       <c r="R8" t="n">
-        <v>7012785</v>
+        <v>7012382</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,39 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R9" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1482,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B10" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,34 +1488,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R10" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -3850,32 +3850,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129700543</v>
+        <v>129701251</v>
       </c>
       <c r="B34" t="n">
-        <v>97645</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575483</v>
+        <v>575332</v>
       </c>
       <c r="R34" t="n">
-        <v>7012735</v>
+        <v>7012509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3947,40 +3947,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129702616</v>
+        <v>129700543</v>
       </c>
       <c r="B35" t="n">
-        <v>92012</v>
+        <v>97645</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575529</v>
+        <v>575483</v>
       </c>
       <c r="R35" t="n">
-        <v>7012502</v>
+        <v>7012735</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4039,10 +4044,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129701251</v>
+        <v>129678425</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4050,37 +4055,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575332</v>
+        <v>575513</v>
       </c>
       <c r="R36" t="n">
-        <v>7012509</v>
+        <v>7012525</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4104,12 +4114,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4124,19 +4134,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129678425</v>
+        <v>129701172</v>
       </c>
       <c r="B37" t="n">
         <v>57736</v>
@@ -4172,17 +4182,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575513</v>
+        <v>575342</v>
       </c>
       <c r="R37" t="n">
-        <v>7012525</v>
+        <v>7012553</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4206,12 +4216,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4226,22 +4241,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129701172</v>
+        <v>129702616</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>92012</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4249,39 +4264,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575342</v>
+        <v>575529</v>
       </c>
       <c r="R38" t="n">
-        <v>7012553</v>
+        <v>7012502</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4314,11 +4319,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6040,50 +6040,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129702749</v>
+        <v>129700911</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>92311</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575545</v>
+        <v>575418</v>
       </c>
       <c r="R56" t="n">
-        <v>7012515</v>
+        <v>7012634</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6116,11 +6111,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6147,10 +6137,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B57" t="n">
-        <v>92311</v>
+        <v>80215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6158,21 +6148,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R57" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6244,45 +6234,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701129</v>
+        <v>129702749</v>
       </c>
       <c r="B58" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575358</v>
+        <v>575545</v>
       </c>
       <c r="R58" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6315,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700955</v>
+        <v>129700923</v>
       </c>
       <c r="B59" t="n">
-        <v>83042</v>
+        <v>82916</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575420</v>
+        <v>575418</v>
       </c>
       <c r="R59" t="n">
-        <v>7012646</v>
+        <v>7012634</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129712553</v>
+        <v>129700955</v>
       </c>
       <c r="B60" t="n">
-        <v>80186</v>
+        <v>83042</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,37 +6449,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575515</v>
+        <v>575420</v>
       </c>
       <c r="R60" t="n">
-        <v>7012371</v>
+        <v>7012646</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6503,12 +6503,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6523,22 +6523,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129712554</v>
+        <v>129701829</v>
       </c>
       <c r="B61" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6546,37 +6546,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575257</v>
+        <v>575378</v>
       </c>
       <c r="R61" t="n">
-        <v>7012718</v>
+        <v>7012599</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6600,12 +6600,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6620,22 +6620,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129701829</v>
+        <v>129712553</v>
       </c>
       <c r="B62" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6643,37 +6643,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575378</v>
+        <v>575515</v>
       </c>
       <c r="R62" t="n">
-        <v>7012599</v>
+        <v>7012371</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6697,12 +6697,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6717,22 +6717,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129700923</v>
+        <v>129712554</v>
       </c>
       <c r="B63" t="n">
-        <v>82916</v>
+        <v>80186</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6740,37 +6740,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575418</v>
+        <v>575257</v>
       </c>
       <c r="R63" t="n">
-        <v>7012634</v>
+        <v>7012718</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6814,12 +6814,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7617,10 +7617,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129712551</v>
+        <v>129700952</v>
       </c>
       <c r="B72" t="n">
-        <v>80186</v>
+        <v>83050</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7628,37 +7628,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>575310</v>
+        <v>575428</v>
       </c>
       <c r="R72" t="n">
-        <v>7012647</v>
+        <v>7012641</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7702,22 +7702,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129700952</v>
+        <v>129712551</v>
       </c>
       <c r="B73" t="n">
-        <v>83050</v>
+        <v>80186</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7725,37 +7725,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>575428</v>
+        <v>575310</v>
       </c>
       <c r="R73" t="n">
-        <v>7012641</v>
+        <v>7012647</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7779,12 +7779,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7799,22 +7799,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B74" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7822,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R74" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,34 +7919,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R75" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678818</v>
+        <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,45 +1189,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erik-elias bodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575350</v>
+        <v>575412</v>
       </c>
       <c r="R7" t="n">
-        <v>7012785</v>
+        <v>7012382</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678421</v>
+        <v>129678818</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,37 +1286,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575412</v>
+        <v>575350</v>
       </c>
       <c r="R8" t="n">
-        <v>7012382</v>
+        <v>7012785</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1391,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R9" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1477,10 +1482,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,39 +1493,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R10" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678445</v>
+        <v>129678416</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575308</v>
+        <v>575334</v>
       </c>
       <c r="R13" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1875,7 +1875,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129678448</v>
+        <v>129678445</v>
       </c>
       <c r="B14" t="n">
         <v>80186</v>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575261</v>
+        <v>575308</v>
       </c>
       <c r="R14" t="n">
-        <v>7012709</v>
+        <v>7012562</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129678416</v>
+        <v>129678448</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575334</v>
+        <v>575261</v>
       </c>
       <c r="R15" t="n">
-        <v>7012592</v>
+        <v>7012709</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2072,7 +2072,7 @@
         <v>129678422</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129678415</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129678418</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>129678419</v>
       </c>
       <c r="B27" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>129678440</v>
       </c>
       <c r="B28" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701251</v>
+        <v>129701172</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,34 +3861,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575332</v>
+        <v>575342</v>
       </c>
       <c r="R34" t="n">
-        <v>7012509</v>
+        <v>7012553</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3921,6 +3926,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3950,7 +3960,7 @@
         <v>129700543</v>
       </c>
       <c r="B35" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4044,10 +4054,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129678425</v>
+        <v>129702616</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>92016</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4055,42 +4065,32 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575513</v>
+        <v>575529</v>
       </c>
       <c r="R36" t="n">
-        <v>7012525</v>
+        <v>7012502</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4114,12 +4114,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4134,22 +4134,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129701172</v>
+        <v>129701251</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4157,39 +4157,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575342</v>
+        <v>575332</v>
       </c>
       <c r="R37" t="n">
-        <v>7012553</v>
+        <v>7012509</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4222,11 +4217,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4253,10 +4243,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129702616</v>
+        <v>129678425</v>
       </c>
       <c r="B38" t="n">
-        <v>92012</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4264,32 +4254,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575529</v>
+        <v>575513</v>
       </c>
       <c r="R38" t="n">
-        <v>7012502</v>
+        <v>7012525</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4333,12 +4333,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
         <v>129701118</v>
       </c>
       <c r="B39" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4539,10 +4539,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702590</v>
+        <v>129712548</v>
       </c>
       <c r="B41" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4550,33 +4550,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575529</v>
+        <v>575383</v>
       </c>
       <c r="R41" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4600,12 +4609,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4620,12 +4629,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4729,10 +4738,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129712548</v>
+        <v>129702590</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>91617</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4740,42 +4749,33 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575383</v>
+        <v>575529</v>
       </c>
       <c r="R43" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4799,12 +4799,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4819,12 +4819,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,39 +5046,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R46" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5111,11 +5106,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5142,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5153,34 +5143,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R47" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5213,6 +5208,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5436,7 +5436,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5750,37 +5750,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R53" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5824,22 +5824,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B54" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R54" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6040,45 +6040,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129700911</v>
+        <v>129702749</v>
       </c>
       <c r="B56" t="n">
-        <v>92311</v>
+        <v>57736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575418</v>
+        <v>575545</v>
       </c>
       <c r="R56" t="n">
-        <v>7012634</v>
+        <v>7012515</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6111,6 +6116,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6137,10 +6147,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B57" t="n">
-        <v>80215</v>
+        <v>92315</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6148,21 +6158,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6172,10 +6182,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6234,50 +6244,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129702749</v>
+        <v>129701129</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575545</v>
+        <v>575358</v>
       </c>
       <c r="R58" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6310,11 +6315,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700923</v>
+        <v>129701829</v>
       </c>
       <c r="B59" t="n">
-        <v>82916</v>
+        <v>91597</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6352,21 +6352,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6376,10 +6376,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>7012634</v>
+        <v>7012599</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129700955</v>
+        <v>129700923</v>
       </c>
       <c r="B60" t="n">
-        <v>83042</v>
+        <v>82916</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6449,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575420</v>
+        <v>575418</v>
       </c>
       <c r="R60" t="n">
-        <v>7012646</v>
+        <v>7012634</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701829</v>
+        <v>129700955</v>
       </c>
       <c r="B61" t="n">
-        <v>91593</v>
+        <v>83042</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6546,21 +6546,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575378</v>
+        <v>575420</v>
       </c>
       <c r="R61" t="n">
-        <v>7012599</v>
+        <v>7012646</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129712553</v>
+        <v>129712554</v>
       </c>
       <c r="B62" t="n">
         <v>80186</v>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575515</v>
+        <v>575257</v>
       </c>
       <c r="R62" t="n">
-        <v>7012371</v>
+        <v>7012718</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6729,7 +6729,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129712554</v>
+        <v>129712553</v>
       </c>
       <c r="B63" t="n">
         <v>80186</v>
@@ -6764,10 +6764,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575257</v>
+        <v>575515</v>
       </c>
       <c r="R63" t="n">
-        <v>7012718</v>
+        <v>7012371</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7025,45 +7025,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702771</v>
+        <v>129701965</v>
       </c>
       <c r="B66" t="n">
-        <v>92311</v>
+        <v>91593</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575545</v>
+        <v>575412</v>
       </c>
       <c r="R66" t="n">
-        <v>7012515</v>
+        <v>7012614</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7122,45 +7122,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702401</v>
+        <v>129702771</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>92315</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575471</v>
+        <v>575545</v>
       </c>
       <c r="R67" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702002</v>
+        <v>129702401</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7230,39 +7230,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575427</v>
+        <v>575471</v>
       </c>
       <c r="R68" t="n">
-        <v>7012593</v>
+        <v>7012565</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7295,11 +7290,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7326,10 +7316,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129701965</v>
+        <v>129702002</v>
       </c>
       <c r="B69" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7337,34 +7327,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575412</v>
+        <v>575427</v>
       </c>
       <c r="R69" t="n">
-        <v>7012614</v>
+        <v>7012593</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7397,6 +7392,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7523,7 +7523,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>129702579</v>
       </c>
       <c r="B75" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -979,45 +979,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678442</v>
+        <v>129678429</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575422</v>
+        <v>575438</v>
       </c>
       <c r="R5" t="n">
-        <v>7012450</v>
+        <v>7012734</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1076,50 +1081,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678429</v>
+        <v>129678442</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>92052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575438</v>
+        <v>575422</v>
       </c>
       <c r="R6" t="n">
-        <v>7012734</v>
+        <v>7012450</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1181,7 +1181,7 @@
         <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,39 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R9" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1482,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B10" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,34 +1488,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R10" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>129678416</v>
       </c>
       <c r="B13" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>129678422</v>
       </c>
       <c r="B16" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129678415</v>
       </c>
       <c r="B21" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129678418</v>
       </c>
       <c r="B22" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678419</v>
+        <v>129678430</v>
       </c>
       <c r="B27" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,34 +3167,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575431</v>
+        <v>575453</v>
       </c>
       <c r="R27" t="n">
-        <v>7012496</v>
+        <v>7012526</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3253,32 +3258,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678440</v>
+        <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>92050</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3288,10 +3293,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575318</v>
+        <v>575431</v>
       </c>
       <c r="R28" t="n">
-        <v>7012643</v>
+        <v>7012496</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3350,50 +3355,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678430</v>
+        <v>129678440</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>92052</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575453</v>
+        <v>575318</v>
       </c>
       <c r="R29" t="n">
-        <v>7012526</v>
+        <v>7012643</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3455,7 +3455,7 @@
         <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701172</v>
+        <v>129678425</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575342</v>
+        <v>575513</v>
       </c>
       <c r="R34" t="n">
-        <v>7012553</v>
+        <v>7012525</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,17 +3920,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3945,44 +3940,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129700543</v>
+        <v>129701251</v>
       </c>
       <c r="B35" t="n">
-        <v>97649</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3992,10 +3987,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575483</v>
+        <v>575332</v>
       </c>
       <c r="R35" t="n">
-        <v>7012735</v>
+        <v>7012509</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4054,10 +4049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129702616</v>
+        <v>129701172</v>
       </c>
       <c r="B36" t="n">
-        <v>92016</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4065,29 +4060,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575529</v>
+        <v>575342</v>
       </c>
       <c r="R36" t="n">
-        <v>7012502</v>
+        <v>7012553</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4120,6 +4125,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4146,32 +4156,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129701251</v>
+        <v>129700543</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>97651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4181,10 +4191,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575332</v>
+        <v>575483</v>
       </c>
       <c r="R37" t="n">
-        <v>7012509</v>
+        <v>7012735</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4243,10 +4253,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129678425</v>
+        <v>129702616</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>92018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4254,42 +4264,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575513</v>
+        <v>575529</v>
       </c>
       <c r="R38" t="n">
-        <v>7012525</v>
+        <v>7012502</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4333,12 +4333,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
         <v>129701118</v>
       </c>
       <c r="B39" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4539,53 +4539,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129712548</v>
+        <v>129702652</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>83035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575383</v>
+        <v>575531</v>
       </c>
       <c r="R41" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4609,12 +4604,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4629,60 +4624,65 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702652</v>
+        <v>129712548</v>
       </c>
       <c r="B42" t="n">
-        <v>83033</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575531</v>
+        <v>575383</v>
       </c>
       <c r="R42" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4706,12 +4706,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4726,12 +4726,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4741,7 +4741,7 @@
         <v>129702590</v>
       </c>
       <c r="B43" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,34 +5046,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R46" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5106,6 +5111,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5132,10 +5142,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,39 +5153,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R47" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5208,11 +5213,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5436,7 +5436,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5739,10 +5739,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B53" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5750,37 +5750,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R53" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5824,22 +5824,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R54" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6040,50 +6040,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129702749</v>
+        <v>129700911</v>
       </c>
       <c r="B56" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575545</v>
+        <v>575418</v>
       </c>
       <c r="R56" t="n">
-        <v>7012515</v>
+        <v>7012634</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6116,11 +6111,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6147,10 +6137,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B57" t="n">
-        <v>92315</v>
+        <v>80215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6158,21 +6148,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R57" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6244,45 +6234,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701129</v>
+        <v>129702749</v>
       </c>
       <c r="B58" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575358</v>
+        <v>575545</v>
       </c>
       <c r="R58" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6315,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,10 +6341,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701829</v>
+        <v>129678427</v>
       </c>
       <c r="B59" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6352,37 +6352,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575378</v>
+        <v>575435</v>
       </c>
       <c r="R59" t="n">
-        <v>7012599</v>
+        <v>7012675</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6406,12 +6411,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6426,22 +6431,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129700923</v>
+        <v>129700955</v>
       </c>
       <c r="B60" t="n">
-        <v>82916</v>
+        <v>83044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6449,21 +6454,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6473,10 +6478,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575418</v>
+        <v>575420</v>
       </c>
       <c r="R60" t="n">
-        <v>7012634</v>
+        <v>7012646</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6535,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129700955</v>
+        <v>129701829</v>
       </c>
       <c r="B61" t="n">
-        <v>83042</v>
+        <v>91599</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6546,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6570,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575420</v>
+        <v>575378</v>
       </c>
       <c r="R61" t="n">
-        <v>7012646</v>
+        <v>7012599</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6632,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129712554</v>
+        <v>129700923</v>
       </c>
       <c r="B62" t="n">
-        <v>80186</v>
+        <v>82918</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6643,37 +6648,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575257</v>
+        <v>575418</v>
       </c>
       <c r="R62" t="n">
-        <v>7012718</v>
+        <v>7012634</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6697,12 +6702,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6717,19 +6722,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129712553</v>
+        <v>129712554</v>
       </c>
       <c r="B63" t="n">
         <v>80186</v>
@@ -6764,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575515</v>
+        <v>575257</v>
       </c>
       <c r="R63" t="n">
-        <v>7012371</v>
+        <v>7012718</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6826,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129678427</v>
+        <v>129712553</v>
       </c>
       <c r="B64" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6837,39 +6842,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575435</v>
+        <v>575515</v>
       </c>
       <c r="R64" t="n">
-        <v>7012675</v>
+        <v>7012371</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7025,10 +7025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129701965</v>
+        <v>129702401</v>
       </c>
       <c r="B66" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575412</v>
+        <v>575471</v>
       </c>
       <c r="R66" t="n">
-        <v>7012614</v>
+        <v>7012565</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7125,7 +7125,7 @@
         <v>129702771</v>
       </c>
       <c r="B67" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702401</v>
+        <v>129701965</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7230,21 +7230,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575471</v>
+        <v>575412</v>
       </c>
       <c r="R68" t="n">
-        <v>7012565</v>
+        <v>7012614</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7426,7 +7426,7 @@
         <v>129702290</v>
       </c>
       <c r="B70" t="n">
-        <v>83033</v>
+        <v>83035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>129700952</v>
       </c>
       <c r="B72" t="n">
-        <v>83050</v>
+        <v>83052</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7811,10 +7811,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7822,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R74" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B75" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,34 +7919,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R75" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -3156,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678430</v>
+        <v>129678419</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,39 +3167,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575453</v>
+        <v>575431</v>
       </c>
       <c r="R27" t="n">
-        <v>7012526</v>
+        <v>7012496</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3258,32 +3253,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678419</v>
+        <v>129678440</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3293,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575431</v>
+        <v>575318</v>
       </c>
       <c r="R28" t="n">
-        <v>7012496</v>
+        <v>7012643</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3355,45 +3350,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678440</v>
+        <v>129678430</v>
       </c>
       <c r="B29" t="n">
-        <v>92052</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575318</v>
+        <v>575453</v>
       </c>
       <c r="R29" t="n">
-        <v>7012643</v>
+        <v>7012526</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4345,48 +4345,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129701118</v>
+        <v>129712552</v>
       </c>
       <c r="B39" t="n">
-        <v>91563</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575354</v>
+        <v>575303</v>
       </c>
       <c r="R39" t="n">
-        <v>7012577</v>
+        <v>7012573</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4410,12 +4410,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4430,60 +4430,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129712552</v>
+        <v>129701118</v>
       </c>
       <c r="B40" t="n">
-        <v>80186</v>
+        <v>91563</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575303</v>
+        <v>575354</v>
       </c>
       <c r="R40" t="n">
-        <v>7012573</v>
+        <v>7012577</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4527,12 +4527,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -6137,45 +6137,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701129</v>
+        <v>129702749</v>
       </c>
       <c r="B57" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575358</v>
+        <v>575545</v>
       </c>
       <c r="R57" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6208,6 +6213,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6234,50 +6244,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129702749</v>
+        <v>129701129</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575545</v>
+        <v>575358</v>
       </c>
       <c r="R58" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6310,11 +6315,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7025,10 +7025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702401</v>
+        <v>129701965</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575471</v>
+        <v>575412</v>
       </c>
       <c r="R66" t="n">
-        <v>7012565</v>
+        <v>7012614</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7122,45 +7122,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702771</v>
+        <v>129702401</v>
       </c>
       <c r="B67" t="n">
-        <v>92317</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575545</v>
+        <v>575471</v>
       </c>
       <c r="R67" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7219,45 +7219,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129701965</v>
+        <v>129702771</v>
       </c>
       <c r="B68" t="n">
-        <v>91595</v>
+        <v>92317</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575412</v>
+        <v>575545</v>
       </c>
       <c r="R68" t="n">
-        <v>7012614</v>
+        <v>7012515</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -979,50 +979,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678429</v>
+        <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>92052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575438</v>
+        <v>575422</v>
       </c>
       <c r="R5" t="n">
-        <v>7012734</v>
+        <v>7012450</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1081,45 +1076,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678442</v>
+        <v>129678429</v>
       </c>
       <c r="B6" t="n">
-        <v>92052</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575422</v>
+        <v>575438</v>
       </c>
       <c r="R6" t="n">
-        <v>7012450</v>
+        <v>7012734</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129678425</v>
+        <v>129701172</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575513</v>
+        <v>575342</v>
       </c>
       <c r="R34" t="n">
-        <v>7012525</v>
+        <v>7012553</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,12 +3920,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3940,12 +3945,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4049,10 +4054,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129701172</v>
+        <v>129702616</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>92018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4060,39 +4065,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575342</v>
+        <v>575529</v>
       </c>
       <c r="R36" t="n">
-        <v>7012553</v>
+        <v>7012502</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4125,11 +4120,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4253,10 +4243,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129702616</v>
+        <v>129678425</v>
       </c>
       <c r="B38" t="n">
-        <v>92018</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4264,32 +4254,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575529</v>
+        <v>575513</v>
       </c>
       <c r="R38" t="n">
-        <v>7012502</v>
+        <v>7012525</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4333,12 +4333,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129701965</v>
+        <v>129702401</v>
       </c>
       <c r="B66" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575412</v>
+        <v>575471</v>
       </c>
       <c r="R66" t="n">
-        <v>7012614</v>
+        <v>7012565</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7122,45 +7122,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702401</v>
+        <v>129702771</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>92317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575471</v>
+        <v>575545</v>
       </c>
       <c r="R67" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7219,45 +7219,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702771</v>
+        <v>129701965</v>
       </c>
       <c r="B68" t="n">
-        <v>92317</v>
+        <v>91595</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575545</v>
+        <v>575412</v>
       </c>
       <c r="R68" t="n">
-        <v>7012515</v>
+        <v>7012614</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678422</v>
+        <v>129678428</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,34 +2080,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575262</v>
+        <v>575416</v>
       </c>
       <c r="R16" t="n">
-        <v>7012542</v>
+        <v>7012774</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,7 +2171,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678414</v>
+        <v>129678422</v>
       </c>
       <c r="B17" t="n">
         <v>91599</v>
@@ -2201,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575411</v>
+        <v>575262</v>
       </c>
       <c r="R17" t="n">
-        <v>7012780</v>
+        <v>7012542</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2263,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678428</v>
+        <v>129678414</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,39 +2279,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575416</v>
+        <v>575411</v>
       </c>
       <c r="R18" t="n">
-        <v>7012774</v>
+        <v>7012780</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678441</v>
+        <v>129678417</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575432</v>
+        <v>575403</v>
       </c>
       <c r="R25" t="n">
-        <v>7012492</v>
+        <v>7012602</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3059,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678417</v>
+        <v>129678441</v>
       </c>
       <c r="B26" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575403</v>
+        <v>575432</v>
       </c>
       <c r="R26" t="n">
-        <v>7012602</v>
+        <v>7012492</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678419</v>
+        <v>129678430</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,34 +3167,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575431</v>
+        <v>575453</v>
       </c>
       <c r="R27" t="n">
-        <v>7012496</v>
+        <v>7012526</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3253,32 +3258,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678440</v>
+        <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3288,10 +3293,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575318</v>
+        <v>575431</v>
       </c>
       <c r="R28" t="n">
-        <v>7012643</v>
+        <v>7012496</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3350,50 +3355,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678430</v>
+        <v>129678440</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>92052</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575453</v>
+        <v>575318</v>
       </c>
       <c r="R29" t="n">
-        <v>7012526</v>
+        <v>7012643</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701172</v>
+        <v>129678425</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575342</v>
+        <v>575513</v>
       </c>
       <c r="R34" t="n">
-        <v>7012553</v>
+        <v>7012525</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,17 +3920,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3945,12 +3940,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4054,10 +4049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129702616</v>
+        <v>129701172</v>
       </c>
       <c r="B36" t="n">
-        <v>92018</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4065,29 +4060,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575529</v>
+        <v>575342</v>
       </c>
       <c r="R36" t="n">
-        <v>7012502</v>
+        <v>7012553</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4120,6 +4125,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4149,7 +4159,7 @@
         <v>129700543</v>
       </c>
       <c r="B37" t="n">
-        <v>97651</v>
+        <v>97661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,10 +4253,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129678425</v>
+        <v>129702616</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>92018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4254,42 +4264,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575513</v>
+        <v>575529</v>
       </c>
       <c r="R38" t="n">
-        <v>7012525</v>
+        <v>7012502</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4333,12 +4333,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4539,34 +4539,30 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702652</v>
+        <v>129702590</v>
       </c>
       <c r="B41" t="n">
-        <v>83035</v>
+        <v>91619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4574,7 +4570,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575531</v>
+        <v>575529</v>
       </c>
       <c r="R41" t="n">
         <v>7012502</v>
@@ -4738,30 +4734,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129702590</v>
+        <v>129702652</v>
       </c>
       <c r="B43" t="n">
-        <v>91619</v>
+        <v>83035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575529</v>
+        <v>575531</v>
       </c>
       <c r="R43" t="n">
         <v>7012502</v>
@@ -6137,50 +6137,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129702749</v>
+        <v>129701129</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575545</v>
+        <v>575358</v>
       </c>
       <c r="R57" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6213,11 +6208,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6244,45 +6234,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701129</v>
+        <v>129702749</v>
       </c>
       <c r="B58" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575358</v>
+        <v>575545</v>
       </c>
       <c r="R58" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6315,6 +6310,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6637,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129700923</v>
+        <v>129712553</v>
       </c>
       <c r="B62" t="n">
-        <v>82918</v>
+        <v>80186</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,37 +6648,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575418</v>
+        <v>575515</v>
       </c>
       <c r="R62" t="n">
-        <v>7012634</v>
+        <v>7012371</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6722,22 +6722,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129712554</v>
+        <v>129700923</v>
       </c>
       <c r="B63" t="n">
-        <v>80186</v>
+        <v>82918</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,37 +6745,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575257</v>
+        <v>575418</v>
       </c>
       <c r="R63" t="n">
-        <v>7012718</v>
+        <v>7012634</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6819,19 +6819,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129712553</v>
+        <v>129712554</v>
       </c>
       <c r="B64" t="n">
         <v>80186</v>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575515</v>
+        <v>575257</v>
       </c>
       <c r="R64" t="n">
-        <v>7012371</v>
+        <v>7012718</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702401</v>
+        <v>129701965</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575471</v>
+        <v>575412</v>
       </c>
       <c r="R66" t="n">
-        <v>7012565</v>
+        <v>7012614</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129701965</v>
+        <v>129702401</v>
       </c>
       <c r="B68" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7230,21 +7230,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575412</v>
+        <v>575471</v>
       </c>
       <c r="R68" t="n">
-        <v>7012614</v>
+        <v>7012565</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7617,10 +7617,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129700952</v>
+        <v>129712551</v>
       </c>
       <c r="B72" t="n">
-        <v>83052</v>
+        <v>80186</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7628,37 +7628,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>575428</v>
+        <v>575310</v>
       </c>
       <c r="R72" t="n">
-        <v>7012641</v>
+        <v>7012647</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7702,22 +7702,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129712551</v>
+        <v>129700952</v>
       </c>
       <c r="B73" t="n">
-        <v>80186</v>
+        <v>83052</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7725,37 +7725,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>575310</v>
+        <v>575428</v>
       </c>
       <c r="R73" t="n">
-        <v>7012647</v>
+        <v>7012641</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7779,12 +7779,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7799,22 +7799,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B74" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7822,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R74" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7908,10 +7908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,34 +7919,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R75" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1391,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R9" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1477,10 +1482,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,39 +1493,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R10" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2569,32 +2569,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678415</v>
+        <v>129678443</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575418</v>
+        <v>575446</v>
       </c>
       <c r="R21" t="n">
-        <v>7012773</v>
+        <v>7012349</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678418</v>
+        <v>129678415</v>
       </c>
       <c r="B22" t="n">
         <v>91599</v>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575428</v>
+        <v>575418</v>
       </c>
       <c r="R22" t="n">
-        <v>7012546</v>
+        <v>7012773</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2763,32 +2763,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129678443</v>
+        <v>129678418</v>
       </c>
       <c r="B23" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575446</v>
+        <v>575428</v>
       </c>
       <c r="R23" t="n">
-        <v>7012349</v>
+        <v>7012546</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678417</v>
+        <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575403</v>
+        <v>575432</v>
       </c>
       <c r="R25" t="n">
-        <v>7012602</v>
+        <v>7012492</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3059,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678441</v>
+        <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575432</v>
+        <v>575403</v>
       </c>
       <c r="R26" t="n">
-        <v>7012492</v>
+        <v>7012602</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129678425</v>
+        <v>129701172</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575513</v>
+        <v>575342</v>
       </c>
       <c r="R34" t="n">
-        <v>7012525</v>
+        <v>7012553</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,12 +3920,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3940,22 +3945,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129701251</v>
+        <v>129678425</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3963,37 +3968,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575332</v>
+        <v>575513</v>
       </c>
       <c r="R35" t="n">
-        <v>7012509</v>
+        <v>7012525</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4017,12 +4027,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4037,22 +4047,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129701172</v>
+        <v>129701251</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4060,39 +4070,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575342</v>
+        <v>575332</v>
       </c>
       <c r="R36" t="n">
-        <v>7012553</v>
+        <v>7012509</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4125,11 +4130,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4539,10 +4539,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702590</v>
+        <v>129712548</v>
       </c>
       <c r="B41" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4550,33 +4550,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575529</v>
+        <v>575383</v>
       </c>
       <c r="R41" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4600,12 +4609,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4620,22 +4629,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129712548</v>
+        <v>129702590</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>91619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4643,42 +4652,33 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575383</v>
+        <v>575529</v>
       </c>
       <c r="R42" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4702,12 +4702,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4722,12 +4722,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,39 +5046,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R46" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5111,11 +5106,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5142,10 +5132,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5153,34 +5143,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R47" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5213,6 +5208,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5750,37 +5750,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R53" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5824,22 +5824,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B54" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R54" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129701965</v>
+        <v>129702002</v>
       </c>
       <c r="B66" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,34 +7036,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575412</v>
+        <v>575427</v>
       </c>
       <c r="R66" t="n">
-        <v>7012614</v>
+        <v>7012593</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7096,6 +7101,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7219,10 +7229,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702401</v>
+        <v>129701965</v>
       </c>
       <c r="B68" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7230,21 +7240,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7254,10 +7264,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575471</v>
+        <v>575412</v>
       </c>
       <c r="R68" t="n">
-        <v>7012565</v>
+        <v>7012614</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7316,10 +7326,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702002</v>
+        <v>129702401</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7327,39 +7337,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575427</v>
+        <v>575471</v>
       </c>
       <c r="R69" t="n">
-        <v>7012593</v>
+        <v>7012565</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7392,11 +7397,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -2569,32 +2569,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678443</v>
+        <v>129678415</v>
       </c>
       <c r="B21" t="n">
-        <v>92052</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575446</v>
+        <v>575418</v>
       </c>
       <c r="R21" t="n">
-        <v>7012349</v>
+        <v>7012773</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678415</v>
+        <v>129678418</v>
       </c>
       <c r="B22" t="n">
         <v>91599</v>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575418</v>
+        <v>575428</v>
       </c>
       <c r="R22" t="n">
-        <v>7012773</v>
+        <v>7012546</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2763,32 +2763,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129678418</v>
+        <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>91599</v>
+        <v>92052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575428</v>
+        <v>575446</v>
       </c>
       <c r="R23" t="n">
-        <v>7012546</v>
+        <v>7012349</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -4831,10 +4831,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129700674</v>
+        <v>129702459</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4842,34 +4842,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575458</v>
+        <v>575495</v>
       </c>
       <c r="R44" t="n">
-        <v>7012679</v>
+        <v>7012552</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4902,6 +4907,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4928,10 +4938,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129702459</v>
+        <v>129700674</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4939,39 +4949,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575495</v>
+        <v>575458</v>
       </c>
       <c r="R45" t="n">
-        <v>7012552</v>
+        <v>7012679</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5004,11 +5009,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5035,10 +5035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,34 +5046,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R46" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5106,6 +5111,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5132,10 +5142,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5143,39 +5153,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R47" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5208,11 +5213,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B53" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5750,37 +5750,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R53" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5824,22 +5824,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,37 +5847,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R54" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5901,12 +5901,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B56" t="n">
-        <v>92317</v>
+        <v>80215</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6051,21 +6051,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R56" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6137,45 +6137,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701129</v>
+        <v>129702749</v>
       </c>
       <c r="B57" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575358</v>
+        <v>575545</v>
       </c>
       <c r="R57" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6208,6 +6213,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6234,50 +6244,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129702749</v>
+        <v>129700911</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>92317</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575545</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>7012515</v>
+        <v>7012634</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6310,11 +6315,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6637,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129712553</v>
+        <v>129700923</v>
       </c>
       <c r="B62" t="n">
-        <v>80186</v>
+        <v>82918</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,37 +6648,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575515</v>
+        <v>575418</v>
       </c>
       <c r="R62" t="n">
-        <v>7012371</v>
+        <v>7012634</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6722,22 +6722,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129700923</v>
+        <v>129712554</v>
       </c>
       <c r="B63" t="n">
-        <v>82918</v>
+        <v>80186</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,37 +6745,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575418</v>
+        <v>575257</v>
       </c>
       <c r="R63" t="n">
-        <v>7012634</v>
+        <v>7012718</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6819,19 +6819,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129712554</v>
+        <v>129712553</v>
       </c>
       <c r="B64" t="n">
         <v>80186</v>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575257</v>
+        <v>575515</v>
       </c>
       <c r="R64" t="n">
-        <v>7012718</v>
+        <v>7012371</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>129678429</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>129678818</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,39 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R9" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1482,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B10" t="n">
-        <v>80186</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,34 +1488,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R10" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129678426</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>129678416</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129678445</v>
       </c>
       <c r="B14" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>129678448</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678428</v>
+        <v>129678422</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>91602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,39 +2080,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575416</v>
+        <v>575262</v>
       </c>
       <c r="R16" t="n">
-        <v>7012774</v>
+        <v>7012542</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2171,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678422</v>
+        <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575262</v>
+        <v>575411</v>
       </c>
       <c r="R17" t="n">
-        <v>7012542</v>
+        <v>7012780</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678414</v>
+        <v>129678428</v>
       </c>
       <c r="B18" t="n">
-        <v>91599</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,34 +2274,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575411</v>
+        <v>575416</v>
       </c>
       <c r="R18" t="n">
-        <v>7012780</v>
+        <v>7012774</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2368,7 +2368,7 @@
         <v>129678431</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>129678433</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129678415</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129678418</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>129678435</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>129678430</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>129678440</v>
       </c>
       <c r="B29" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>129678434</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129678446</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129678437</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701172</v>
+        <v>129678425</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3886,17 +3886,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575342</v>
+        <v>575513</v>
       </c>
       <c r="R34" t="n">
-        <v>7012553</v>
+        <v>7012525</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,17 +3920,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3945,22 +3940,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129678425</v>
+        <v>129701251</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3968,42 +3963,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575513</v>
+        <v>575332</v>
       </c>
       <c r="R35" t="n">
-        <v>7012525</v>
+        <v>7012509</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4027,12 +4017,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4047,22 +4037,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129701251</v>
+        <v>129701172</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4070,34 +4060,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575332</v>
+        <v>575342</v>
       </c>
       <c r="R36" t="n">
-        <v>7012509</v>
+        <v>7012553</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4130,6 +4125,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4156,45 +4156,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129700543</v>
+        <v>129702616</v>
       </c>
       <c r="B37" t="n">
-        <v>97661</v>
+        <v>92021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575483</v>
+        <v>575529</v>
       </c>
       <c r="R37" t="n">
-        <v>7012735</v>
+        <v>7012502</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4253,40 +4253,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129702616</v>
+        <v>129700543</v>
       </c>
       <c r="B38" t="n">
-        <v>92018</v>
+        <v>97665</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575529</v>
+        <v>575483</v>
       </c>
       <c r="R38" t="n">
-        <v>7012502</v>
+        <v>7012735</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4345,48 +4350,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129712552</v>
+        <v>129701118</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>91566</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575303</v>
+        <v>575354</v>
       </c>
       <c r="R39" t="n">
-        <v>7012573</v>
+        <v>7012577</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4410,12 +4415,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4430,60 +4435,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129701118</v>
+        <v>129712552</v>
       </c>
       <c r="B40" t="n">
-        <v>91563</v>
+        <v>80189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575354</v>
+        <v>575303</v>
       </c>
       <c r="R40" t="n">
-        <v>7012577</v>
+        <v>7012573</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4507,12 +4512,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4527,22 +4532,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129712548</v>
+        <v>129702590</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>91622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4550,42 +4555,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575383</v>
+        <v>575529</v>
       </c>
       <c r="R41" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4609,12 +4605,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4629,42 +4625,46 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702590</v>
+        <v>129702652</v>
       </c>
       <c r="B42" t="n">
-        <v>91619</v>
+        <v>83038</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575529</v>
+        <v>575531</v>
       </c>
       <c r="R42" t="n">
         <v>7012502</v>
@@ -4734,48 +4734,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129702652</v>
+        <v>129712548</v>
       </c>
       <c r="B43" t="n">
-        <v>83035</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575531</v>
+        <v>575383</v>
       </c>
       <c r="R43" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4799,12 +4804,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4819,12 +4824,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4834,7 +4839,7 @@
         <v>129702459</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4941,7 +4946,7 @@
         <v>129700674</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5035,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5046,39 +5051,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R46" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5111,11 +5111,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5142,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5153,34 +5148,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R47" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5213,6 +5213,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5239,10 +5244,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129700728</v>
+        <v>129702707</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5270,14 +5275,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575445</v>
+        <v>575543</v>
       </c>
       <c r="R48" t="n">
-        <v>7012641</v>
+        <v>7012496</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5336,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129702707</v>
+        <v>129700728</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5367,14 +5372,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575543</v>
+        <v>575445</v>
       </c>
       <c r="R49" t="n">
-        <v>7012496</v>
+        <v>7012641</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5436,7 +5441,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5533,7 +5538,7 @@
         <v>129700719</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5640,7 +5645,7 @@
         <v>129712549</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5739,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5750,37 +5755,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R53" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5804,12 +5809,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5824,22 +5829,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B54" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5847,37 +5852,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R54" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5901,12 +5906,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5921,12 +5926,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5936,7 +5941,7 @@
         <v>129701902</v>
       </c>
       <c r="B55" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6040,10 +6045,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B56" t="n">
-        <v>80215</v>
+        <v>92320</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6051,21 +6056,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6075,10 +6080,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R56" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6137,50 +6142,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129702749</v>
+        <v>129701129</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>80218</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575545</v>
+        <v>575358</v>
       </c>
       <c r="R57" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6213,11 +6213,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6244,45 +6239,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700911</v>
+        <v>129702749</v>
       </c>
       <c r="B58" t="n">
-        <v>92317</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575545</v>
       </c>
       <c r="R58" t="n">
-        <v>7012634</v>
+        <v>7012515</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6315,6 +6315,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6341,10 +6346,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129678427</v>
+        <v>129701829</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>91602</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6352,42 +6357,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575435</v>
+        <v>575378</v>
       </c>
       <c r="R59" t="n">
-        <v>7012675</v>
+        <v>7012599</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6411,12 +6411,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6431,22 +6431,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129700955</v>
+        <v>129678427</v>
       </c>
       <c r="B60" t="n">
-        <v>83044</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,37 +6454,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575420</v>
+        <v>575435</v>
       </c>
       <c r="R60" t="n">
-        <v>7012646</v>
+        <v>7012675</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6508,12 +6513,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6528,22 +6533,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701829</v>
+        <v>129700955</v>
       </c>
       <c r="B61" t="n">
-        <v>91599</v>
+        <v>83047</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,21 +6556,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6575,10 +6580,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575378</v>
+        <v>575420</v>
       </c>
       <c r="R61" t="n">
-        <v>7012599</v>
+        <v>7012646</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6640,7 +6645,7 @@
         <v>129700923</v>
       </c>
       <c r="B62" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6737,7 +6742,7 @@
         <v>129712554</v>
       </c>
       <c r="B63" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6834,7 +6839,7 @@
         <v>129712553</v>
       </c>
       <c r="B64" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6931,7 +6936,7 @@
         <v>129702542</v>
       </c>
       <c r="B65" t="n">
-        <v>80222</v>
+        <v>80225</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7025,10 +7030,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702002</v>
+        <v>129701965</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>91598</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7036,39 +7041,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575427</v>
+        <v>575412</v>
       </c>
       <c r="R66" t="n">
-        <v>7012593</v>
+        <v>7012614</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7101,11 +7101,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7135,7 +7130,7 @@
         <v>129702771</v>
       </c>
       <c r="B67" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7229,10 +7224,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129701965</v>
+        <v>129702401</v>
       </c>
       <c r="B68" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7240,21 +7235,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7264,10 +7259,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575412</v>
+        <v>575471</v>
       </c>
       <c r="R68" t="n">
-        <v>7012614</v>
+        <v>7012565</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7326,10 +7321,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702401</v>
+        <v>129702002</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7337,34 +7332,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575471</v>
+        <v>575427</v>
       </c>
       <c r="R69" t="n">
-        <v>7012565</v>
+        <v>7012593</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7397,6 +7397,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7426,7 +7431,7 @@
         <v>129702290</v>
       </c>
       <c r="B70" t="n">
-        <v>83035</v>
+        <v>83038</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7523,7 +7528,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7620,7 +7625,7 @@
         <v>129712551</v>
       </c>
       <c r="B72" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7717,7 +7722,7 @@
         <v>129700952</v>
       </c>
       <c r="B73" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7811,10 +7816,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7822,34 +7827,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R74" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7908,10 +7913,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B75" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7919,34 +7924,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R75" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678421</v>
+        <v>129678818</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,37 +1189,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575412</v>
+        <v>575350</v>
       </c>
       <c r="R7" t="n">
-        <v>7012382</v>
+        <v>7012785</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678818</v>
+        <v>129678421</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,45 +1294,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Erik-elias bodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575350</v>
+        <v>575412</v>
       </c>
       <c r="R8" t="n">
-        <v>7012785</v>
+        <v>7012382</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1391,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R9" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1477,10 +1482,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,39 +1493,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R10" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B53" t="n">
-        <v>91602</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5755,37 +5755,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R53" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5829,22 +5829,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>91602</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,37 +5852,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R54" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5926,12 +5926,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>129678429</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678818</v>
+        <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,45 +1189,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erik-elias bodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575350</v>
+        <v>575412</v>
       </c>
       <c r="R7" t="n">
-        <v>7012785</v>
+        <v>7012382</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,10 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678421</v>
+        <v>129678818</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1294,37 +1286,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575412</v>
+        <v>575350</v>
       </c>
       <c r="R8" t="n">
-        <v>7012382</v>
+        <v>7012785</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>80192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,39 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R9" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1482,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B10" t="n">
-        <v>80189</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,34 +1488,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R10" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>129678426</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678416</v>
+        <v>129678445</v>
       </c>
       <c r="B13" t="n">
-        <v>91602</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1789,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575334</v>
+        <v>575308</v>
       </c>
       <c r="R13" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129678445</v>
+        <v>129678448</v>
       </c>
       <c r="B14" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575308</v>
+        <v>575261</v>
       </c>
       <c r="R14" t="n">
-        <v>7012562</v>
+        <v>7012709</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129678448</v>
+        <v>129678416</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>91605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575261</v>
+        <v>575334</v>
       </c>
       <c r="R15" t="n">
-        <v>7012709</v>
+        <v>7012592</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2072,7 +2072,7 @@
         <v>129678422</v>
       </c>
       <c r="B16" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129678428</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>129678431</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>129678433</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>129678415</v>
       </c>
       <c r="B21" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>129678418</v>
       </c>
       <c r="B22" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>129678435</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678441</v>
+        <v>129678417</v>
       </c>
       <c r="B25" t="n">
-        <v>92055</v>
+        <v>91605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575432</v>
+        <v>575403</v>
       </c>
       <c r="R25" t="n">
-        <v>7012492</v>
+        <v>7012602</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3059,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678417</v>
+        <v>129678441</v>
       </c>
       <c r="B26" t="n">
-        <v>91602</v>
+        <v>92058</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575403</v>
+        <v>575432</v>
       </c>
       <c r="R26" t="n">
-        <v>7012602</v>
+        <v>7012492</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678430</v>
+        <v>129678419</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,39 +3167,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575453</v>
+        <v>575431</v>
       </c>
       <c r="R27" t="n">
-        <v>7012526</v>
+        <v>7012496</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3258,32 +3253,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678419</v>
+        <v>129678440</v>
       </c>
       <c r="B28" t="n">
-        <v>91602</v>
+        <v>92058</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3293,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575431</v>
+        <v>575318</v>
       </c>
       <c r="R28" t="n">
-        <v>7012496</v>
+        <v>7012643</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3355,45 +3350,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678440</v>
+        <v>129678430</v>
       </c>
       <c r="B29" t="n">
-        <v>92055</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575318</v>
+        <v>575453</v>
       </c>
       <c r="R29" t="n">
-        <v>7012643</v>
+        <v>7012526</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3455,7 +3455,7 @@
         <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>129678434</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129678446</v>
       </c>
       <c r="B32" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129678437</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129678425</v>
+        <v>129701251</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,42 +3861,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575513</v>
+        <v>575332</v>
       </c>
       <c r="R34" t="n">
-        <v>7012525</v>
+        <v>7012509</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,12 +3915,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3940,22 +3935,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129701251</v>
+        <v>129701172</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3963,34 +3958,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575332</v>
+        <v>575342</v>
       </c>
       <c r="R35" t="n">
-        <v>7012509</v>
+        <v>7012553</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4023,6 +4023,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4049,10 +4054,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129701172</v>
+        <v>129678425</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,17 +4090,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575342</v>
+        <v>575513</v>
       </c>
       <c r="R36" t="n">
-        <v>7012553</v>
+        <v>7012525</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4119,17 +4124,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,57 +4144,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129702616</v>
+        <v>129700543</v>
       </c>
       <c r="B37" t="n">
-        <v>92021</v>
+        <v>97668</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575529</v>
+        <v>575483</v>
       </c>
       <c r="R37" t="n">
-        <v>7012502</v>
+        <v>7012735</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4253,45 +4253,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129700543</v>
+        <v>129702616</v>
       </c>
       <c r="B38" t="n">
-        <v>97665</v>
+        <v>92024</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575483</v>
+        <v>575529</v>
       </c>
       <c r="R38" t="n">
-        <v>7012735</v>
+        <v>7012502</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4350,48 +4350,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129701118</v>
+        <v>129712552</v>
       </c>
       <c r="B39" t="n">
-        <v>91566</v>
+        <v>80192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575354</v>
+        <v>575303</v>
       </c>
       <c r="R39" t="n">
-        <v>7012577</v>
+        <v>7012573</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4435,60 +4435,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129712552</v>
+        <v>129701118</v>
       </c>
       <c r="B40" t="n">
-        <v>80189</v>
+        <v>91569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575303</v>
+        <v>575354</v>
       </c>
       <c r="R40" t="n">
-        <v>7012573</v>
+        <v>7012577</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4532,22 +4532,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702590</v>
+        <v>129712548</v>
       </c>
       <c r="B41" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4555,33 +4555,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575529</v>
+        <v>575383</v>
       </c>
       <c r="R41" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4605,12 +4614,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4625,46 +4634,42 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702652</v>
+        <v>129702590</v>
       </c>
       <c r="B42" t="n">
-        <v>83038</v>
+        <v>91625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4672,7 +4677,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575531</v>
+        <v>575529</v>
       </c>
       <c r="R42" t="n">
         <v>7012502</v>
@@ -4734,53 +4739,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129712548</v>
+        <v>129702652</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>83041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575383</v>
+        <v>575531</v>
       </c>
       <c r="R43" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4824,12 +4824,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         <v>129702459</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>129700674</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>129702105</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129702707</v>
+        <v>129700728</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5275,14 +5275,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575543</v>
+        <v>575445</v>
       </c>
       <c r="R48" t="n">
-        <v>7012496</v>
+        <v>7012641</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129700728</v>
+        <v>129702707</v>
       </c>
       <c r="B49" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5372,14 +5372,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575445</v>
+        <v>575543</v>
       </c>
       <c r="R49" t="n">
-        <v>7012641</v>
+        <v>7012496</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5441,7 +5441,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>129700719</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>129712549</v>
       </c>
       <c r="B52" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>91605</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5755,37 +5755,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R53" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5829,22 +5829,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B54" t="n">
-        <v>91602</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,37 +5852,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R54" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5926,12 +5926,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5941,7 +5941,7 @@
         <v>129701902</v>
       </c>
       <c r="B55" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>129700911</v>
       </c>
       <c r="B56" t="n">
-        <v>92320</v>
+        <v>92323</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>129701129</v>
       </c>
       <c r="B57" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>129702749</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6346,10 +6346,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129701829</v>
+        <v>129700923</v>
       </c>
       <c r="B59" t="n">
-        <v>91602</v>
+        <v>82924</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R59" t="n">
-        <v>7012599</v>
+        <v>7012634</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6443,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129678427</v>
+        <v>129712554</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>80192</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,39 +6454,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575435</v>
+        <v>575257</v>
       </c>
       <c r="R60" t="n">
-        <v>7012675</v>
+        <v>7012718</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6513,12 +6508,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6545,10 +6540,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129700955</v>
+        <v>129712553</v>
       </c>
       <c r="B61" t="n">
-        <v>83047</v>
+        <v>80192</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6556,37 +6551,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575420</v>
+        <v>575515</v>
       </c>
       <c r="R61" t="n">
-        <v>7012646</v>
+        <v>7012371</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6610,12 +6605,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6630,22 +6625,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129700923</v>
+        <v>129701829</v>
       </c>
       <c r="B62" t="n">
-        <v>82921</v>
+        <v>91605</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575418</v>
+        <v>575378</v>
       </c>
       <c r="R62" t="n">
-        <v>7012634</v>
+        <v>7012599</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6739,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129712554</v>
+        <v>129700955</v>
       </c>
       <c r="B63" t="n">
-        <v>80189</v>
+        <v>83050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6750,37 +6745,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575257</v>
+        <v>575420</v>
       </c>
       <c r="R63" t="n">
-        <v>7012718</v>
+        <v>7012646</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6804,12 +6799,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6824,22 +6819,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129712553</v>
+        <v>129678427</v>
       </c>
       <c r="B64" t="n">
-        <v>80189</v>
+        <v>57740</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,34 +6842,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575515</v>
+        <v>575435</v>
       </c>
       <c r="R64" t="n">
-        <v>7012371</v>
+        <v>7012675</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6936,7 +6936,7 @@
         <v>129702542</v>
       </c>
       <c r="B65" t="n">
-        <v>80225</v>
+        <v>80228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7030,45 +7030,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129701965</v>
+        <v>129702771</v>
       </c>
       <c r="B66" t="n">
-        <v>91598</v>
+        <v>92323</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575412</v>
+        <v>575545</v>
       </c>
       <c r="R66" t="n">
-        <v>7012614</v>
+        <v>7012515</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7127,45 +7127,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702771</v>
+        <v>129701965</v>
       </c>
       <c r="B67" t="n">
-        <v>92320</v>
+        <v>91601</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575545</v>
+        <v>575412</v>
       </c>
       <c r="R67" t="n">
-        <v>7012515</v>
+        <v>7012614</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7227,7 +7227,7 @@
         <v>129702401</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>129702002</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>129702290</v>
       </c>
       <c r="B70" t="n">
-        <v>83038</v>
+        <v>83041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7622,10 +7622,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129712551</v>
+        <v>129700952</v>
       </c>
       <c r="B72" t="n">
-        <v>80189</v>
+        <v>83058</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7633,37 +7633,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>575310</v>
+        <v>575428</v>
       </c>
       <c r="R72" t="n">
-        <v>7012647</v>
+        <v>7012641</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7707,22 +7707,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129700952</v>
+        <v>129712551</v>
       </c>
       <c r="B73" t="n">
-        <v>83055</v>
+        <v>80192</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7730,37 +7730,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>575428</v>
+        <v>575310</v>
       </c>
       <c r="R73" t="n">
-        <v>7012641</v>
+        <v>7012647</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7804,12 +7804,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
         <v>129702579</v>
       </c>
       <c r="B74" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>129701072</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -4350,48 +4350,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129712552</v>
+        <v>129701118</v>
       </c>
       <c r="B39" t="n">
-        <v>80192</v>
+        <v>91569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575303</v>
+        <v>575354</v>
       </c>
       <c r="R39" t="n">
-        <v>7012573</v>
+        <v>7012577</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4435,60 +4435,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129701118</v>
+        <v>129712552</v>
       </c>
       <c r="B40" t="n">
-        <v>91569</v>
+        <v>80192</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575354</v>
+        <v>575303</v>
       </c>
       <c r="R40" t="n">
-        <v>7012577</v>
+        <v>7012573</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4532,22 +4532,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129712548</v>
+        <v>129702590</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>91625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4555,42 +4555,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575383</v>
+        <v>575529</v>
       </c>
       <c r="R41" t="n">
-        <v>7012472</v>
+        <v>7012502</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4614,12 +4605,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4634,42 +4625,46 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702590</v>
+        <v>129702652</v>
       </c>
       <c r="B42" t="n">
-        <v>91625</v>
+        <v>83041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4677,7 +4672,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575529</v>
+        <v>575531</v>
       </c>
       <c r="R42" t="n">
         <v>7012502</v>
@@ -4739,48 +4734,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129702652</v>
+        <v>129712548</v>
       </c>
       <c r="B43" t="n">
-        <v>83041</v>
+        <v>57740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575531</v>
+        <v>575383</v>
       </c>
       <c r="R43" t="n">
-        <v>7012502</v>
+        <v>7012472</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4824,12 +4824,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6045,10 +6045,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B56" t="n">
-        <v>92323</v>
+        <v>80221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6056,21 +6056,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R56" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6142,45 +6142,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129701129</v>
+        <v>129702749</v>
       </c>
       <c r="B57" t="n">
-        <v>80221</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575358</v>
+        <v>575545</v>
       </c>
       <c r="R57" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6213,6 +6218,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6239,50 +6249,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129702749</v>
+        <v>129700911</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575545</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>7012515</v>
+        <v>7012634</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6315,11 +6320,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701251</v>
+        <v>129701172</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,34 +3861,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575332</v>
+        <v>575342</v>
       </c>
       <c r="R34" t="n">
-        <v>7012509</v>
+        <v>7012553</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3921,6 +3926,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3947,7 +3957,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129701172</v>
+        <v>129678425</v>
       </c>
       <c r="B35" t="n">
         <v>57740</v>
@@ -3983,17 +3993,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575342</v>
+        <v>575513</v>
       </c>
       <c r="R35" t="n">
-        <v>7012553</v>
+        <v>7012525</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4017,17 +4027,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4042,65 +4047,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129678425</v>
+        <v>129700543</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>97668</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575513</v>
+        <v>575483</v>
       </c>
       <c r="R36" t="n">
-        <v>7012525</v>
+        <v>7012735</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,44 +4144,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129700543</v>
+        <v>129701251</v>
       </c>
       <c r="B37" t="n">
-        <v>97668</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575483</v>
+        <v>575332</v>
       </c>
       <c r="R37" t="n">
-        <v>7012735</v>
+        <v>7012509</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,34 +5051,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R46" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5111,6 +5116,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5137,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5148,39 +5158,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R47" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5213,11 +5218,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6045,45 +6045,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129701129</v>
+        <v>129702749</v>
       </c>
       <c r="B56" t="n">
-        <v>80221</v>
+        <v>57740</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575358</v>
+        <v>575545</v>
       </c>
       <c r="R56" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6116,6 +6121,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,50 +6152,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129702749</v>
+        <v>129700911</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>92323</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575545</v>
+        <v>575418</v>
       </c>
       <c r="R57" t="n">
-        <v>7012515</v>
+        <v>7012634</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6218,11 +6223,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B58" t="n">
-        <v>92323</v>
+        <v>80221</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6260,21 +6260,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6284,10 +6284,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R58" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6346,10 +6346,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129700923</v>
+        <v>129700955</v>
       </c>
       <c r="B59" t="n">
-        <v>82924</v>
+        <v>83050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575418</v>
+        <v>575420</v>
       </c>
       <c r="R59" t="n">
-        <v>7012634</v>
+        <v>7012646</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6443,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129712554</v>
+        <v>129678427</v>
       </c>
       <c r="B60" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,34 +6454,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575257</v>
+        <v>575435</v>
       </c>
       <c r="R60" t="n">
-        <v>7012718</v>
+        <v>7012675</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6508,12 +6513,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6540,10 +6545,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129712553</v>
+        <v>129701829</v>
       </c>
       <c r="B61" t="n">
-        <v>80192</v>
+        <v>91605</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6551,37 +6556,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575515</v>
+        <v>575378</v>
       </c>
       <c r="R61" t="n">
-        <v>7012371</v>
+        <v>7012599</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6605,12 +6610,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6625,22 +6630,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129701829</v>
+        <v>129700923</v>
       </c>
       <c r="B62" t="n">
-        <v>91605</v>
+        <v>82924</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6648,21 +6653,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R62" t="n">
-        <v>7012599</v>
+        <v>7012634</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6734,10 +6739,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129700955</v>
+        <v>129712554</v>
       </c>
       <c r="B63" t="n">
-        <v>83050</v>
+        <v>80192</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,37 +6750,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575420</v>
+        <v>575257</v>
       </c>
       <c r="R63" t="n">
-        <v>7012646</v>
+        <v>7012718</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6799,12 +6804,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6819,22 +6824,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129678427</v>
+        <v>129712553</v>
       </c>
       <c r="B64" t="n">
-        <v>57740</v>
+        <v>80192</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,39 +6847,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575435</v>
+        <v>575515</v>
       </c>
       <c r="R64" t="n">
-        <v>7012675</v>
+        <v>7012371</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
         <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>129678421</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B9" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,34 +1391,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R9" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1477,10 +1482,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,39 +1493,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R10" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>129678445</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129678448</v>
+        <v>129678416</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575261</v>
+        <v>575334</v>
       </c>
       <c r="R14" t="n">
-        <v>7012709</v>
+        <v>7012592</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129678416</v>
+        <v>129678448</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>80193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575334</v>
+        <v>575261</v>
       </c>
       <c r="R15" t="n">
-        <v>7012592</v>
+        <v>7012709</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678422</v>
+        <v>129678428</v>
       </c>
       <c r="B16" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,34 +2080,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575262</v>
+        <v>575416</v>
       </c>
       <c r="R16" t="n">
-        <v>7012542</v>
+        <v>7012774</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,10 +2171,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678414</v>
+        <v>129678422</v>
       </c>
       <c r="B17" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575411</v>
+        <v>575262</v>
       </c>
       <c r="R17" t="n">
-        <v>7012780</v>
+        <v>7012542</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2263,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678428</v>
+        <v>129678414</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,39 +2279,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575416</v>
+        <v>575411</v>
       </c>
       <c r="R18" t="n">
-        <v>7012774</v>
+        <v>7012780</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2569,10 +2569,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678415</v>
+        <v>129678418</v>
       </c>
       <c r="B21" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575418</v>
+        <v>575428</v>
       </c>
       <c r="R21" t="n">
-        <v>7012773</v>
+        <v>7012546</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678418</v>
+        <v>129678415</v>
       </c>
       <c r="B22" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575428</v>
+        <v>575418</v>
       </c>
       <c r="R22" t="n">
-        <v>7012546</v>
+        <v>7012773</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2766,7 +2766,7 @@
         <v>129678443</v>
       </c>
       <c r="B23" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678417</v>
+        <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
+        <v>92059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575403</v>
+        <v>575432</v>
       </c>
       <c r="R25" t="n">
-        <v>7012602</v>
+        <v>7012492</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3059,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678441</v>
+        <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>92058</v>
+        <v>91606</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575432</v>
+        <v>575403</v>
       </c>
       <c r="R26" t="n">
-        <v>7012492</v>
+        <v>7012602</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678419</v>
+        <v>129678430</v>
       </c>
       <c r="B27" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,34 +3167,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575431</v>
+        <v>575453</v>
       </c>
       <c r="R27" t="n">
-        <v>7012496</v>
+        <v>7012526</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3253,32 +3258,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678440</v>
+        <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>92058</v>
+        <v>91606</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3288,10 +3293,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575318</v>
+        <v>575431</v>
       </c>
       <c r="R28" t="n">
-        <v>7012643</v>
+        <v>7012496</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3350,50 +3355,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678430</v>
+        <v>129678440</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>92059</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575453</v>
+        <v>575318</v>
       </c>
       <c r="R29" t="n">
-        <v>7012526</v>
+        <v>7012643</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3455,7 +3455,7 @@
         <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129678446</v>
       </c>
       <c r="B32" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701172</v>
+        <v>129701251</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,39 +3861,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575342</v>
+        <v>575332</v>
       </c>
       <c r="R34" t="n">
-        <v>7012553</v>
+        <v>7012509</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3926,11 +3921,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3957,7 +3947,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129678425</v>
+        <v>129701172</v>
       </c>
       <c r="B35" t="n">
         <v>57740</v>
@@ -3993,17 +3983,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575513</v>
+        <v>575342</v>
       </c>
       <c r="R35" t="n">
-        <v>7012525</v>
+        <v>7012553</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4027,12 +4017,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4047,12 +4042,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4062,7 +4057,7 @@
         <v>129700543</v>
       </c>
       <c r="B36" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4156,10 +4151,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129701251</v>
+        <v>129702616</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>92025</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4167,34 +4162,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6040186</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575332</v>
+        <v>575529</v>
       </c>
       <c r="R37" t="n">
-        <v>7012509</v>
+        <v>7012502</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4253,10 +4248,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129702616</v>
+        <v>129678425</v>
       </c>
       <c r="B38" t="n">
-        <v>92024</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4264,37 +4259,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575529</v>
+        <v>575513</v>
       </c>
       <c r="R38" t="n">
-        <v>7012502</v>
+        <v>7012525</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4318,12 +4318,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4338,12 +4338,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4353,7 +4353,7 @@
         <v>129701118</v>
       </c>
       <c r="B39" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>129712552</v>
       </c>
       <c r="B40" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4544,30 +4544,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702590</v>
+        <v>129702652</v>
       </c>
       <c r="B41" t="n">
-        <v>91625</v>
+        <v>83042</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4575,7 +4579,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575529</v>
+        <v>575531</v>
       </c>
       <c r="R41" t="n">
         <v>7012502</v>
@@ -4637,34 +4641,30 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702652</v>
+        <v>129702590</v>
       </c>
       <c r="B42" t="n">
-        <v>83041</v>
+        <v>91626</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575531</v>
+        <v>575529</v>
       </c>
       <c r="R42" t="n">
         <v>7012502</v>
@@ -4946,7 +4946,7 @@
         <v>129700674</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129702105</v>
+        <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,39 +5051,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575427</v>
+        <v>575431</v>
       </c>
       <c r="R46" t="n">
-        <v>7012592</v>
+        <v>7012562</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5116,11 +5111,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5147,10 +5137,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129701504</v>
+        <v>129702105</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,34 +5148,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575431</v>
+        <v>575427</v>
       </c>
       <c r="R47" t="n">
-        <v>7012562</v>
+        <v>7012592</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5218,6 +5213,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,7 +5247,7 @@
         <v>129700728</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>129702707</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>129701024</v>
       </c>
       <c r="B53" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>129712558</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6045,50 +6045,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129702749</v>
+        <v>129701129</v>
       </c>
       <c r="B56" t="n">
-        <v>57740</v>
+        <v>80222</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575545</v>
+        <v>575358</v>
       </c>
       <c r="R56" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6121,11 +6116,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6152,45 +6142,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129700911</v>
+        <v>129702749</v>
       </c>
       <c r="B57" t="n">
-        <v>92323</v>
+        <v>57740</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575418</v>
+        <v>575545</v>
       </c>
       <c r="R57" t="n">
-        <v>7012634</v>
+        <v>7012515</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6223,6 +6218,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6249,10 +6249,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B58" t="n">
-        <v>80221</v>
+        <v>92324</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6260,21 +6260,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6284,10 +6284,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R58" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6349,7 +6349,7 @@
         <v>129700955</v>
       </c>
       <c r="B59" t="n">
-        <v>83050</v>
+        <v>83051</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6443,10 +6443,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129678427</v>
+        <v>129701829</v>
       </c>
       <c r="B60" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6454,42 +6454,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575435</v>
+        <v>575378</v>
       </c>
       <c r="R60" t="n">
-        <v>7012675</v>
+        <v>7012599</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6513,12 +6508,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6533,22 +6528,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129701829</v>
+        <v>129700923</v>
       </c>
       <c r="B61" t="n">
-        <v>91605</v>
+        <v>82925</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6556,21 +6551,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6580,10 +6575,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575378</v>
+        <v>575418</v>
       </c>
       <c r="R61" t="n">
-        <v>7012599</v>
+        <v>7012634</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6642,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129700923</v>
+        <v>129712554</v>
       </c>
       <c r="B62" t="n">
-        <v>82924</v>
+        <v>80193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,37 +6648,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575418</v>
+        <v>575257</v>
       </c>
       <c r="R62" t="n">
-        <v>7012634</v>
+        <v>7012718</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6707,12 +6702,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6727,22 +6722,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129712554</v>
+        <v>129712553</v>
       </c>
       <c r="B63" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6774,10 +6769,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575257</v>
+        <v>575515</v>
       </c>
       <c r="R63" t="n">
-        <v>7012718</v>
+        <v>7012371</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6836,10 +6831,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129712553</v>
+        <v>129678427</v>
       </c>
       <c r="B64" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,34 +6842,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575515</v>
+        <v>575435</v>
       </c>
       <c r="R64" t="n">
-        <v>7012371</v>
+        <v>7012675</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6936,7 +6936,7 @@
         <v>129702542</v>
       </c>
       <c r="B65" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7030,45 +7030,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702771</v>
+        <v>129702401</v>
       </c>
       <c r="B66" t="n">
-        <v>92323</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575545</v>
+        <v>575471</v>
       </c>
       <c r="R66" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129701965</v>
+        <v>129702002</v>
       </c>
       <c r="B67" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7138,34 +7138,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575412</v>
+        <v>575427</v>
       </c>
       <c r="R67" t="n">
-        <v>7012614</v>
+        <v>7012593</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7198,6 +7203,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7224,45 +7234,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702401</v>
+        <v>129702771</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>92324</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575471</v>
+        <v>575545</v>
       </c>
       <c r="R68" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7321,10 +7331,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702002</v>
+        <v>129701965</v>
       </c>
       <c r="B69" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7332,39 +7342,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575427</v>
+        <v>575412</v>
       </c>
       <c r="R69" t="n">
-        <v>7012593</v>
+        <v>7012614</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7397,11 +7402,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7431,7 +7431,7 @@
         <v>129702290</v>
       </c>
       <c r="B70" t="n">
-        <v>83041</v>
+        <v>83042</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7622,10 +7622,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129700952</v>
+        <v>129712551</v>
       </c>
       <c r="B72" t="n">
-        <v>83058</v>
+        <v>80193</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7633,37 +7633,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>575428</v>
+        <v>575310</v>
       </c>
       <c r="R72" t="n">
-        <v>7012641</v>
+        <v>7012647</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7707,22 +7707,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129712551</v>
+        <v>129700952</v>
       </c>
       <c r="B73" t="n">
-        <v>80192</v>
+        <v>83059</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7730,37 +7730,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>575310</v>
+        <v>575428</v>
       </c>
       <c r="R73" t="n">
-        <v>7012647</v>
+        <v>7012641</v>
       </c>
       <c r="S73" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7804,12 +7804,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7819,7 +7819,7 @@
         <v>129702579</v>
       </c>
       <c r="B74" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>129701072</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -979,45 +979,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678442</v>
+        <v>129678429</v>
       </c>
       <c r="B5" t="n">
-        <v>92059</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575422</v>
+        <v>575438</v>
       </c>
       <c r="R5" t="n">
-        <v>7012450</v>
+        <v>7012734</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1076,50 +1081,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678429</v>
+        <v>129678442</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>92059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575438</v>
+        <v>575422</v>
       </c>
       <c r="R6" t="n">
-        <v>7012734</v>
+        <v>7012450</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678428</v>
+        <v>129678422</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,39 +2080,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575416</v>
+        <v>575262</v>
       </c>
       <c r="R16" t="n">
-        <v>7012774</v>
+        <v>7012542</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2171,7 +2166,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678422</v>
+        <v>129678414</v>
       </c>
       <c r="B17" t="n">
         <v>91606</v>
@@ -2206,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575262</v>
+        <v>575411</v>
       </c>
       <c r="R17" t="n">
-        <v>7012542</v>
+        <v>7012780</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2268,10 +2263,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678414</v>
+        <v>129678428</v>
       </c>
       <c r="B18" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,34 +2274,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575411</v>
+        <v>575416</v>
       </c>
       <c r="R18" t="n">
-        <v>7012780</v>
+        <v>7012774</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678418</v>
+        <v>129678415</v>
       </c>
       <c r="B21" t="n">
         <v>91606</v>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575428</v>
+        <v>575418</v>
       </c>
       <c r="R21" t="n">
-        <v>7012546</v>
+        <v>7012773</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678415</v>
+        <v>129678418</v>
       </c>
       <c r="B22" t="n">
         <v>91606</v>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575418</v>
+        <v>575428</v>
       </c>
       <c r="R22" t="n">
-        <v>7012773</v>
+        <v>7012546</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678441</v>
+        <v>129678417</v>
       </c>
       <c r="B25" t="n">
-        <v>92059</v>
+        <v>91606</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575432</v>
+        <v>575403</v>
       </c>
       <c r="R25" t="n">
-        <v>7012492</v>
+        <v>7012602</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3059,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678417</v>
+        <v>129678441</v>
       </c>
       <c r="B26" t="n">
-        <v>91606</v>
+        <v>92059</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575403</v>
+        <v>575432</v>
       </c>
       <c r="R26" t="n">
-        <v>7012602</v>
+        <v>7012492</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -4544,34 +4544,30 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702652</v>
+        <v>129702590</v>
       </c>
       <c r="B41" t="n">
-        <v>83042</v>
+        <v>91626</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4579,7 +4575,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575531</v>
+        <v>575529</v>
       </c>
       <c r="R41" t="n">
         <v>7012502</v>
@@ -4641,30 +4637,34 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702590</v>
+        <v>129702652</v>
       </c>
       <c r="B42" t="n">
-        <v>91626</v>
+        <v>83042</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575529</v>
+        <v>575531</v>
       </c>
       <c r="R42" t="n">
         <v>7012502</v>
@@ -7030,45 +7030,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702401</v>
+        <v>129702771</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>92324</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575471</v>
+        <v>575545</v>
       </c>
       <c r="R66" t="n">
-        <v>7012565</v>
+        <v>7012515</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702002</v>
+        <v>129701965</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7138,39 +7138,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575427</v>
+        <v>575412</v>
       </c>
       <c r="R67" t="n">
-        <v>7012593</v>
+        <v>7012614</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7203,11 +7198,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7234,45 +7224,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702771</v>
+        <v>129702401</v>
       </c>
       <c r="B68" t="n">
-        <v>92324</v>
+        <v>79088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575545</v>
+        <v>575471</v>
       </c>
       <c r="R68" t="n">
-        <v>7012515</v>
+        <v>7012565</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7331,10 +7321,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129701965</v>
+        <v>129702002</v>
       </c>
       <c r="B69" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7342,34 +7332,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575412</v>
+        <v>575427</v>
       </c>
       <c r="R69" t="n">
-        <v>7012614</v>
+        <v>7012593</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7402,6 +7397,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7622,10 +7622,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129712551</v>
+        <v>129700952</v>
       </c>
       <c r="B72" t="n">
-        <v>80193</v>
+        <v>83059</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7633,37 +7633,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>575310</v>
+        <v>575428</v>
       </c>
       <c r="R72" t="n">
-        <v>7012647</v>
+        <v>7012641</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7687,12 +7687,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7707,22 +7707,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129700952</v>
+        <v>129712551</v>
       </c>
       <c r="B73" t="n">
-        <v>83059</v>
+        <v>80193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7730,37 +7730,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>575428</v>
+        <v>575310</v>
       </c>
       <c r="R73" t="n">
-        <v>7012641</v>
+        <v>7012647</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7804,12 +7804,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -1380,10 +1380,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678438</v>
+        <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,39 +1391,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575264</v>
+        <v>575305</v>
       </c>
       <c r="R9" t="n">
-        <v>7012697</v>
+        <v>7012630</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1482,10 +1477,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678444</v>
+        <v>129678438</v>
       </c>
       <c r="B10" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1493,34 +1488,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575305</v>
+        <v>575264</v>
       </c>
       <c r="R10" t="n">
-        <v>7012630</v>
+        <v>7012697</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678422</v>
+        <v>129678428</v>
       </c>
       <c r="B16" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,34 +2080,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575262</v>
+        <v>575416</v>
       </c>
       <c r="R16" t="n">
-        <v>7012542</v>
+        <v>7012774</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2166,7 +2171,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678414</v>
+        <v>129678422</v>
       </c>
       <c r="B17" t="n">
         <v>91606</v>
@@ -2201,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575411</v>
+        <v>575262</v>
       </c>
       <c r="R17" t="n">
-        <v>7012780</v>
+        <v>7012542</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2263,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678428</v>
+        <v>129678414</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,39 +2279,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575416</v>
+        <v>575411</v>
       </c>
       <c r="R18" t="n">
-        <v>7012774</v>
+        <v>7012780</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678415</v>
+        <v>129678418</v>
       </c>
       <c r="B21" t="n">
         <v>91606</v>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575418</v>
+        <v>575428</v>
       </c>
       <c r="R21" t="n">
-        <v>7012773</v>
+        <v>7012546</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678418</v>
+        <v>129678415</v>
       </c>
       <c r="B22" t="n">
         <v>91606</v>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575428</v>
+        <v>575418</v>
       </c>
       <c r="R22" t="n">
-        <v>7012546</v>
+        <v>7012773</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2962,32 +2962,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678417</v>
+        <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>91606</v>
+        <v>92059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575403</v>
+        <v>575432</v>
       </c>
       <c r="R25" t="n">
-        <v>7012602</v>
+        <v>7012492</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3059,32 +3059,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678441</v>
+        <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>92059</v>
+        <v>91606</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575432</v>
+        <v>575403</v>
       </c>
       <c r="R26" t="n">
-        <v>7012492</v>
+        <v>7012602</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3156,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678430</v>
+        <v>129678419</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,39 +3167,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575453</v>
+        <v>575431</v>
       </c>
       <c r="R27" t="n">
-        <v>7012526</v>
+        <v>7012496</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3258,32 +3253,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678419</v>
+        <v>129678440</v>
       </c>
       <c r="B28" t="n">
-        <v>91606</v>
+        <v>92059</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3293,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575431</v>
+        <v>575318</v>
       </c>
       <c r="R28" t="n">
-        <v>7012496</v>
+        <v>7012643</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3355,45 +3350,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678440</v>
+        <v>129678430</v>
       </c>
       <c r="B29" t="n">
-        <v>92059</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575318</v>
+        <v>575453</v>
       </c>
       <c r="R29" t="n">
-        <v>7012643</v>
+        <v>7012526</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -4151,10 +4151,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129702616</v>
+        <v>129678425</v>
       </c>
       <c r="B37" t="n">
-        <v>92025</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4162,37 +4162,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575529</v>
+        <v>575513</v>
       </c>
       <c r="R37" t="n">
-        <v>7012502</v>
+        <v>7012525</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4216,12 +4221,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4236,22 +4241,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129678425</v>
+        <v>129702616</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>92025</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4259,42 +4264,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6040186</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575513</v>
+        <v>575529</v>
       </c>
       <c r="R38" t="n">
-        <v>7012525</v>
+        <v>7012502</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4318,12 +4318,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4338,12 +4338,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4544,30 +4544,34 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129702590</v>
+        <v>129702652</v>
       </c>
       <c r="B41" t="n">
-        <v>91626</v>
+        <v>83042</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4575,7 +4579,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575529</v>
+        <v>575531</v>
       </c>
       <c r="R41" t="n">
         <v>7012502</v>
@@ -4637,34 +4641,30 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702652</v>
+        <v>129702590</v>
       </c>
       <c r="B42" t="n">
-        <v>83042</v>
+        <v>91626</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575531</v>
+        <v>575529</v>
       </c>
       <c r="R42" t="n">
         <v>7012502</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -979,50 +979,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678429</v>
+        <v>129678442</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>92076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575438</v>
+        <v>575422</v>
       </c>
       <c r="R5" t="n">
-        <v>7012734</v>
+        <v>7012450</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1081,45 +1076,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678442</v>
+        <v>129678429</v>
       </c>
       <c r="B6" t="n">
-        <v>92059</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575422</v>
+        <v>575438</v>
       </c>
       <c r="R6" t="n">
-        <v>7012450</v>
+        <v>7012734</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678421</v>
+        <v>129678818</v>
       </c>
       <c r="B7" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,37 +1189,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575412</v>
+        <v>575350</v>
       </c>
       <c r="R7" t="n">
-        <v>7012382</v>
+        <v>7012785</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,10 +1283,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678818</v>
+        <v>129678421</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>91623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1286,45 +1294,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Erik-elias bodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575350</v>
+        <v>575412</v>
       </c>
       <c r="R8" t="n">
-        <v>7012785</v>
+        <v>7012382</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>129678444</v>
       </c>
       <c r="B9" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>129678420</v>
       </c>
       <c r="B11" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>129678445</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>129678416</v>
       </c>
       <c r="B14" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>129678448</v>
       </c>
       <c r="B15" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678422</v>
+        <v>129678414</v>
       </c>
       <c r="B17" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575262</v>
+        <v>575411</v>
       </c>
       <c r="R17" t="n">
-        <v>7012542</v>
+        <v>7012780</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2268,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678414</v>
+        <v>129678422</v>
       </c>
       <c r="B18" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575411</v>
+        <v>575262</v>
       </c>
       <c r="R18" t="n">
-        <v>7012780</v>
+        <v>7012542</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2569,32 +2569,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678418</v>
+        <v>129678443</v>
       </c>
       <c r="B21" t="n">
-        <v>91606</v>
+        <v>92076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575428</v>
+        <v>575446</v>
       </c>
       <c r="R21" t="n">
-        <v>7012546</v>
+        <v>7012349</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2669,7 +2669,7 @@
         <v>129678415</v>
       </c>
       <c r="B22" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2763,32 +2763,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129678443</v>
+        <v>129678418</v>
       </c>
       <c r="B23" t="n">
-        <v>92059</v>
+        <v>91623</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575446</v>
+        <v>575428</v>
       </c>
       <c r="R23" t="n">
-        <v>7012349</v>
+        <v>7012546</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2965,7 +2965,7 @@
         <v>129678441</v>
       </c>
       <c r="B25" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>129678417</v>
       </c>
       <c r="B26" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3156,32 +3156,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678419</v>
+        <v>129678440</v>
       </c>
       <c r="B27" t="n">
-        <v>91606</v>
+        <v>92076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575431</v>
+        <v>575318</v>
       </c>
       <c r="R27" t="n">
-        <v>7012496</v>
+        <v>7012643</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3253,32 +3253,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678440</v>
+        <v>129678419</v>
       </c>
       <c r="B28" t="n">
-        <v>92059</v>
+        <v>91623</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575318</v>
+        <v>575431</v>
       </c>
       <c r="R28" t="n">
-        <v>7012643</v>
+        <v>7012496</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3455,7 +3455,7 @@
         <v>129678423</v>
       </c>
       <c r="B30" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129678446</v>
       </c>
       <c r="B32" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129701251</v>
+        <v>129678425</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3861,37 +3861,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575332</v>
+        <v>575513</v>
       </c>
       <c r="R34" t="n">
-        <v>7012509</v>
+        <v>7012525</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3915,12 +3920,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3935,22 +3940,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129701172</v>
+        <v>129701251</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,39 +3963,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575342</v>
+        <v>575332</v>
       </c>
       <c r="R35" t="n">
-        <v>7012553</v>
+        <v>7012509</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4023,11 +4023,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4054,45 +4049,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129700543</v>
+        <v>129701172</v>
       </c>
       <c r="B36" t="n">
-        <v>97669</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575483</v>
+        <v>575342</v>
       </c>
       <c r="R36" t="n">
-        <v>7012735</v>
+        <v>7012553</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4125,6 +4125,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4151,53 +4156,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129678425</v>
+        <v>129700543</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>97686</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575513</v>
+        <v>575483</v>
       </c>
       <c r="R37" t="n">
-        <v>7012525</v>
+        <v>7012735</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4221,12 +4221,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4241,12 +4241,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4256,7 +4256,7 @@
         <v>129702616</v>
       </c>
       <c r="B38" t="n">
-        <v>92025</v>
+        <v>92042</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>129701118</v>
       </c>
       <c r="B39" t="n">
-        <v>91570</v>
+        <v>91587</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>129712552</v>
       </c>
       <c r="B40" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>129702652</v>
       </c>
       <c r="B41" t="n">
-        <v>83042</v>
+        <v>83048</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>129702590</v>
       </c>
       <c r="B42" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>129700674</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>129701504</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129700728</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>129702707</v>
       </c>
       <c r="B49" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>129700982</v>
       </c>
       <c r="B50" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129701024</v>
+        <v>129712558</v>
       </c>
       <c r="B53" t="n">
-        <v>91606</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5755,37 +5755,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575367</v>
+        <v>575222</v>
       </c>
       <c r="R53" t="n">
-        <v>7012641</v>
+        <v>7012818</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5829,22 +5829,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129712558</v>
+        <v>129701024</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>91623</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,37 +5852,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575222</v>
+        <v>575367</v>
       </c>
       <c r="R54" t="n">
-        <v>7012818</v>
+        <v>7012641</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5926,12 +5926,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6045,10 +6045,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129701129</v>
+        <v>129700911</v>
       </c>
       <c r="B56" t="n">
-        <v>80222</v>
+        <v>92341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6056,21 +6056,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575358</v>
+        <v>575418</v>
       </c>
       <c r="R56" t="n">
-        <v>7012565</v>
+        <v>7012634</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6249,10 +6249,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700911</v>
+        <v>129701129</v>
       </c>
       <c r="B58" t="n">
-        <v>92324</v>
+        <v>80223</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6260,21 +6260,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6284,10 +6284,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575358</v>
       </c>
       <c r="R58" t="n">
-        <v>7012634</v>
+        <v>7012565</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6349,7 +6349,7 @@
         <v>129700955</v>
       </c>
       <c r="B59" t="n">
-        <v>83051</v>
+        <v>83057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129701829</v>
       </c>
       <c r="B60" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>129700923</v>
       </c>
       <c r="B61" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6637,10 +6637,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129712554</v>
+        <v>129712553</v>
       </c>
       <c r="B62" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575257</v>
+        <v>575515</v>
       </c>
       <c r="R62" t="n">
-        <v>7012718</v>
+        <v>7012371</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6734,10 +6734,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129712553</v>
+        <v>129678427</v>
       </c>
       <c r="B63" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6745,34 +6745,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575515</v>
+        <v>575435</v>
       </c>
       <c r="R63" t="n">
-        <v>7012371</v>
+        <v>7012675</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6799,12 +6804,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6831,10 +6836,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129678427</v>
+        <v>129712554</v>
       </c>
       <c r="B64" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6842,39 +6847,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575435</v>
+        <v>575257</v>
       </c>
       <c r="R64" t="n">
-        <v>7012675</v>
+        <v>7012718</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6936,7 +6936,7 @@
         <v>129702542</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>129702771</v>
       </c>
       <c r="B66" t="n">
-        <v>92324</v>
+        <v>92341</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129701965</v>
+        <v>129702401</v>
       </c>
       <c r="B67" t="n">
-        <v>91602</v>
+        <v>79089</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7138,21 +7138,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575412</v>
+        <v>575471</v>
       </c>
       <c r="R67" t="n">
-        <v>7012614</v>
+        <v>7012565</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7224,10 +7224,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129702401</v>
+        <v>129701965</v>
       </c>
       <c r="B68" t="n">
-        <v>79088</v>
+        <v>91619</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7235,21 +7235,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575471</v>
+        <v>575412</v>
       </c>
       <c r="R68" t="n">
-        <v>7012565</v>
+        <v>7012614</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7431,7 +7431,7 @@
         <v>129702290</v>
       </c>
       <c r="B70" t="n">
-        <v>83042</v>
+        <v>83048</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>129702355</v>
       </c>
       <c r="B71" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>129700952</v>
       </c>
       <c r="B72" t="n">
-        <v>83059</v>
+        <v>83065</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>129712551</v>
       </c>
       <c r="B73" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129702579</v>
+        <v>129701072</v>
       </c>
       <c r="B74" t="n">
-        <v>91606</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7827,34 +7827,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575529</v>
+        <v>575348</v>
       </c>
       <c r="R74" t="n">
-        <v>7012502</v>
+        <v>7012619</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -7913,10 +7913,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129701072</v>
+        <v>129702579</v>
       </c>
       <c r="B75" t="n">
-        <v>79088</v>
+        <v>91623</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7924,34 +7924,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575348</v>
+        <v>575529</v>
       </c>
       <c r="R75" t="n">
-        <v>7012619</v>
+        <v>7012502</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128580870</v>
+        <v>129700955</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575492</v>
+        <v>575420</v>
       </c>
       <c r="R2" t="n">
-        <v>7012557</v>
+        <v>7012646</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128580868</v>
+        <v>129700982</v>
       </c>
       <c r="B3" t="n">
-        <v>82898</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575396</v>
+        <v>575401</v>
       </c>
       <c r="R3" t="n">
-        <v>7012488</v>
+        <v>7012650</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128580869</v>
+        <v>129701965</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,45 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575492</v>
+        <v>575412</v>
       </c>
       <c r="R4" t="n">
-        <v>7012557</v>
+        <v>7012614</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -942,17 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>i ett par gamla granar.</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,60 +954,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Malmsten</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129678442</v>
+        <v>129702355</v>
       </c>
       <c r="B5" t="n">
-        <v>92076</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575422</v>
+        <v>575474</v>
       </c>
       <c r="R5" t="n">
-        <v>7012450</v>
+        <v>7012588</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129678429</v>
+        <v>129678414</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1087,39 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575438</v>
+        <v>575411</v>
       </c>
       <c r="R6" t="n">
-        <v>7012734</v>
+        <v>7012780</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1178,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129678818</v>
+        <v>129678415</v>
       </c>
       <c r="B7" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,45 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Erik-elias bodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575350</v>
+        <v>575418</v>
       </c>
       <c r="R7" t="n">
-        <v>7012785</v>
+        <v>7012773</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129678421</v>
+        <v>129678416</v>
       </c>
       <c r="B8" t="n">
-        <v>91623</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575412</v>
+        <v>575334</v>
       </c>
       <c r="R8" t="n">
-        <v>7012382</v>
+        <v>7012592</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1380,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129678444</v>
+        <v>129678417</v>
       </c>
       <c r="B9" t="n">
-        <v>80194</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1391,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1415,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575305</v>
+        <v>575403</v>
       </c>
       <c r="R9" t="n">
-        <v>7012630</v>
+        <v>7012602</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1477,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129678438</v>
+        <v>129678418</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1488,39 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575264</v>
+        <v>575428</v>
       </c>
       <c r="R10" t="n">
-        <v>7012697</v>
+        <v>7012546</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1579,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129678420</v>
+        <v>129678419</v>
       </c>
       <c r="B11" t="n">
-        <v>91623</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575423</v>
+        <v>575431</v>
       </c>
       <c r="R11" t="n">
-        <v>7012448</v>
+        <v>7012496</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1676,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129678426</v>
+        <v>129678420</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1687,39 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575467</v>
+        <v>575423</v>
       </c>
       <c r="R12" t="n">
-        <v>7012676</v>
+        <v>7012448</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1778,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129678445</v>
+        <v>129678421</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1789,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575308</v>
+        <v>575412</v>
       </c>
       <c r="R13" t="n">
-        <v>7012562</v>
+        <v>7012382</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1875,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129678416</v>
+        <v>129678422</v>
       </c>
       <c r="B14" t="n">
-        <v>91623</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575334</v>
+        <v>575262</v>
       </c>
       <c r="R14" t="n">
-        <v>7012592</v>
+        <v>7012542</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1972,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129678448</v>
+        <v>129678423</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575261</v>
+        <v>575229</v>
       </c>
       <c r="R15" t="n">
-        <v>7012709</v>
+        <v>7012609</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2069,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129678428</v>
+        <v>129701024</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,42 +2044,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575416</v>
+        <v>575367</v>
       </c>
       <c r="R16" t="n">
-        <v>7012774</v>
+        <v>7012641</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2139,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2159,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129678414</v>
+        <v>129701829</v>
       </c>
       <c r="B17" t="n">
-        <v>91623</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2202,17 +2161,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575411</v>
+        <v>575378</v>
       </c>
       <c r="R17" t="n">
-        <v>7012780</v>
+        <v>7012599</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2236,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2256,22 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129678422</v>
+        <v>129702579</v>
       </c>
       <c r="B18" t="n">
-        <v>91623</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2299,17 +2258,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575262</v>
+        <v>575529</v>
       </c>
       <c r="R18" t="n">
-        <v>7012542</v>
+        <v>7012502</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2333,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2353,22 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129678431</v>
+        <v>129678440</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>92369</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2376,39 +2335,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575424</v>
+        <v>575318</v>
       </c>
       <c r="R19" t="n">
-        <v>7012521</v>
+        <v>7012643</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2467,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129678433</v>
+        <v>129678441</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>92369</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2478,39 +2432,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575295</v>
+        <v>575432</v>
       </c>
       <c r="R20" t="n">
-        <v>7012515</v>
+        <v>7012492</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2569,14 +2518,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129678443</v>
+        <v>129678442</v>
       </c>
       <c r="B21" t="n">
-        <v>92076</v>
+        <v>92369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2604,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575446</v>
+        <v>575422</v>
       </c>
       <c r="R21" t="n">
-        <v>7012349</v>
+        <v>7012450</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2666,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129678415</v>
+        <v>129678443</v>
       </c>
       <c r="B22" t="n">
-        <v>91623</v>
+        <v>92369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2677,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2701,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575418</v>
+        <v>575446</v>
       </c>
       <c r="R22" t="n">
-        <v>7012773</v>
+        <v>7012349</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2763,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129678418</v>
+        <v>128580868</v>
       </c>
       <c r="B23" t="n">
-        <v>91623</v>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,37 +2723,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575428</v>
+        <v>575396</v>
       </c>
       <c r="R23" t="n">
-        <v>7012546</v>
+        <v>7012488</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2828,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2848,22 +2797,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129678435</v>
+        <v>129700923</v>
       </c>
       <c r="B24" t="n">
-        <v>57740</v>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2871,42 +2820,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575269</v>
+        <v>575418</v>
       </c>
       <c r="R24" t="n">
-        <v>7012673</v>
+        <v>7012634</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2930,12 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2950,60 +2894,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129678441</v>
+        <v>129700911</v>
       </c>
       <c r="B25" t="n">
-        <v>92076</v>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575432</v>
+        <v>575418</v>
       </c>
       <c r="R25" t="n">
-        <v>7012492</v>
+        <v>7012634</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3027,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3047,60 +2991,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129678417</v>
+        <v>129702771</v>
       </c>
       <c r="B26" t="n">
-        <v>91623</v>
+        <v>92632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575403</v>
+        <v>575545</v>
       </c>
       <c r="R26" t="n">
-        <v>7012602</v>
+        <v>7012515</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3124,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3144,60 +3088,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129678440</v>
+        <v>129701118</v>
       </c>
       <c r="B27" t="n">
-        <v>92076</v>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575318</v>
+        <v>575354</v>
       </c>
       <c r="R27" t="n">
-        <v>7012643</v>
+        <v>7012577</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3221,12 +3165,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3241,60 +3185,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129678419</v>
+        <v>128580870</v>
       </c>
       <c r="B28" t="n">
-        <v>91623</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575431</v>
+        <v>575492</v>
       </c>
       <c r="R28" t="n">
-        <v>7012496</v>
+        <v>7012557</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3318,12 +3262,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3338,65 +3282,60 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129678430</v>
+        <v>129700674</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575453</v>
+        <v>575458</v>
       </c>
       <c r="R29" t="n">
-        <v>7012526</v>
+        <v>7012679</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3420,12 +3359,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3440,60 +3379,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129678423</v>
+        <v>129700728</v>
       </c>
       <c r="B30" t="n">
-        <v>91623</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575229</v>
+        <v>575445</v>
       </c>
       <c r="R30" t="n">
-        <v>7012609</v>
+        <v>7012641</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3517,12 +3456,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3537,65 +3476,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129678434</v>
+        <v>129701072</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575250</v>
+        <v>575348</v>
       </c>
       <c r="R31" t="n">
-        <v>7012580</v>
+        <v>7012619</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3619,12 +3553,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3639,60 +3573,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129678446</v>
+        <v>129701251</v>
       </c>
       <c r="B32" t="n">
-        <v>80194</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575354</v>
+        <v>575332</v>
       </c>
       <c r="R32" t="n">
-        <v>7012563</v>
+        <v>7012509</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3716,12 +3650,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3736,65 +3670,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129678437</v>
+        <v>129701504</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575201</v>
+        <v>575431</v>
       </c>
       <c r="R33" t="n">
-        <v>7012827</v>
+        <v>7012562</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3818,12 +3747,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3838,65 +3767,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129678425</v>
+        <v>129702401</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575513</v>
+        <v>575471</v>
       </c>
       <c r="R34" t="n">
-        <v>7012525</v>
+        <v>7012565</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3920,12 +3844,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3940,62 +3864,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129701172</v>
+        <v>129702707</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575342</v>
+        <v>575543</v>
       </c>
       <c r="R35" t="n">
-        <v>7012553</v>
+        <v>7012496</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4028,11 +3947,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4059,48 +3973,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129700543</v>
+        <v>129712558</v>
       </c>
       <c r="B36" t="n">
-        <v>97691</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575483</v>
+        <v>575222</v>
       </c>
       <c r="R36" t="n">
-        <v>7012735</v>
+        <v>7012818</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4124,12 +4038,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,57 +4058,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129702616</v>
+        <v>129702290</v>
       </c>
       <c r="B37" t="n">
-        <v>92047</v>
+        <v>83290</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040186</v>
+        <v>6439</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575529</v>
+        <v>575476</v>
       </c>
       <c r="R37" t="n">
-        <v>7012502</v>
+        <v>7012589</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4253,45 +4167,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129701251</v>
+        <v>129702652</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>83290</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575332</v>
+        <v>575531</v>
       </c>
       <c r="R38" t="n">
-        <v>7012509</v>
+        <v>7012502</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4350,32 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129701118</v>
+        <v>129700952</v>
       </c>
       <c r="B39" t="n">
-        <v>91592</v>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575354</v>
+        <v>575428</v>
       </c>
       <c r="R39" t="n">
-        <v>7012577</v>
+        <v>7012641</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4447,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129712552</v>
+        <v>129678444</v>
       </c>
       <c r="B40" t="n">
-        <v>80194</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4482,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575303</v>
+        <v>575305</v>
       </c>
       <c r="R40" t="n">
-        <v>7012573</v>
+        <v>7012630</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4512,12 +4426,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4544,10 +4458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129712548</v>
+        <v>129678445</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4555,39 +4469,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575383</v>
+        <v>575308</v>
       </c>
       <c r="R41" t="n">
-        <v>7012472</v>
+        <v>7012562</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -4614,12 +4523,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4646,10 +4555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129702590</v>
+        <v>129678446</v>
       </c>
       <c r="B42" t="n">
-        <v>91648</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,33 +4566,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575529</v>
+        <v>575354</v>
       </c>
       <c r="R42" t="n">
-        <v>7012502</v>
+        <v>7012563</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4707,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4727,60 +4640,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129702652</v>
+        <v>129678447</v>
       </c>
       <c r="B43" t="n">
-        <v>83048</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575531</v>
+        <v>575514</v>
       </c>
       <c r="R43" t="n">
-        <v>7012502</v>
+        <v>7012365</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4804,12 +4717,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4824,22 +4737,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129702459</v>
+        <v>129678448</v>
       </c>
       <c r="B44" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4847,42 +4760,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575495</v>
+        <v>575261</v>
       </c>
       <c r="R44" t="n">
-        <v>7012552</v>
+        <v>7012709</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4906,17 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4931,22 +4834,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129700674</v>
+        <v>129712551</v>
       </c>
       <c r="B45" t="n">
-        <v>79089</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4954,37 +4857,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575458</v>
+        <v>575310</v>
       </c>
       <c r="R45" t="n">
-        <v>7012679</v>
+        <v>7012647</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5008,12 +4911,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5028,22 +4931,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129702105</v>
+        <v>129712552</v>
       </c>
       <c r="B46" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5051,42 +4954,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575427</v>
+        <v>575303</v>
       </c>
       <c r="R46" t="n">
-        <v>7012592</v>
+        <v>7012573</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5110,17 +5008,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5135,22 +5028,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129701504</v>
+        <v>129712553</v>
       </c>
       <c r="B47" t="n">
-        <v>79089</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,37 +5051,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575431</v>
+        <v>575515</v>
       </c>
       <c r="R47" t="n">
-        <v>7012562</v>
+        <v>7012371</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5212,12 +5105,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5232,22 +5125,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129700728</v>
+        <v>129712554</v>
       </c>
       <c r="B48" t="n">
-        <v>79089</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5255,37 +5148,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575445</v>
+        <v>575257</v>
       </c>
       <c r="R48" t="n">
-        <v>7012641</v>
+        <v>7012718</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5309,12 +5202,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5329,57 +5222,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129702707</v>
+        <v>129701129</v>
       </c>
       <c r="B49" t="n">
-        <v>79089</v>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575543</v>
+        <v>575358</v>
       </c>
       <c r="R49" t="n">
-        <v>7012496</v>
+        <v>7012565</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5438,45 +5331,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129700982</v>
+        <v>129702542</v>
       </c>
       <c r="B50" t="n">
-        <v>91624</v>
+        <v>80468</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>575401</v>
+        <v>575538</v>
       </c>
       <c r="R50" t="n">
-        <v>7012650</v>
+        <v>7012552</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5535,10 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129700719</v>
+        <v>128580869</v>
       </c>
       <c r="B51" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5564,24 +5457,27 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>575458</v>
+        <v>575492</v>
       </c>
       <c r="R51" t="n">
-        <v>7012663</v>
+        <v>7012557</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5605,17 +5501,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack gran</t>
+          <t>i ett par gamla granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5630,22 +5526,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anders Malmsten</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129712549</v>
+        <v>129678425</v>
       </c>
       <c r="B52" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5682,10 +5578,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>575210</v>
+        <v>575513</v>
       </c>
       <c r="R52" t="n">
-        <v>7012839</v>
+        <v>7012525</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -5712,12 +5608,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5744,10 +5640,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129712558</v>
+        <v>129678426</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5755,34 +5651,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>575222</v>
+        <v>575467</v>
       </c>
       <c r="R53" t="n">
-        <v>7012818</v>
+        <v>7012676</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -5809,12 +5710,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5841,10 +5742,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129701024</v>
+        <v>129678427</v>
       </c>
       <c r="B54" t="n">
-        <v>91628</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5852,37 +5753,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>575367</v>
+        <v>575435</v>
       </c>
       <c r="R54" t="n">
-        <v>7012641</v>
+        <v>7012675</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5906,12 +5812,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5926,22 +5832,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129701902</v>
+        <v>129678428</v>
       </c>
       <c r="B55" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5974,17 +5880,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>575412</v>
+        <v>575416</v>
       </c>
       <c r="R55" t="n">
-        <v>7012629</v>
+        <v>7012774</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6008,17 +5914,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6033,60 +5934,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129701129</v>
+        <v>129678429</v>
       </c>
       <c r="B56" t="n">
-        <v>80223</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>575358</v>
+        <v>575438</v>
       </c>
       <c r="R56" t="n">
-        <v>7012565</v>
+        <v>7012734</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6110,12 +6016,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6130,22 +6036,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129702749</v>
+        <v>129678430</v>
       </c>
       <c r="B57" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6173,22 +6079,22 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>575545</v>
+        <v>575453</v>
       </c>
       <c r="R57" t="n">
-        <v>7012515</v>
+        <v>7012526</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6212,17 +6118,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack gran</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6237,60 +6138,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129700911</v>
+        <v>129678431</v>
       </c>
       <c r="B58" t="n">
-        <v>92346</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>575418</v>
+        <v>575424</v>
       </c>
       <c r="R58" t="n">
-        <v>7012634</v>
+        <v>7012521</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6314,12 +6220,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,22 +6240,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129678427</v>
+        <v>129678432</v>
       </c>
       <c r="B59" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6386,10 +6292,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>575435</v>
+        <v>575377</v>
       </c>
       <c r="R59" t="n">
-        <v>7012675</v>
+        <v>7012468</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -6448,10 +6354,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129712554</v>
+        <v>129678433</v>
       </c>
       <c r="B60" t="n">
-        <v>80194</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6459,34 +6365,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>575257</v>
+        <v>575295</v>
       </c>
       <c r="R60" t="n">
-        <v>7012718</v>
+        <v>7012515</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -6513,12 +6424,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6545,10 +6456,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129712553</v>
+        <v>129678434</v>
       </c>
       <c r="B61" t="n">
-        <v>80194</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6556,34 +6467,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>575515</v>
+        <v>575250</v>
       </c>
       <c r="R61" t="n">
-        <v>7012371</v>
+        <v>7012580</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -6610,12 +6526,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6642,10 +6558,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129700923</v>
+        <v>129678435</v>
       </c>
       <c r="B62" t="n">
-        <v>82931</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6653,37 +6569,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>575418</v>
+        <v>575269</v>
       </c>
       <c r="R62" t="n">
-        <v>7012634</v>
+        <v>7012673</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6707,12 +6628,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6727,22 +6648,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129700955</v>
+        <v>129678436</v>
       </c>
       <c r="B63" t="n">
-        <v>83057</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6750,37 +6671,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>575420</v>
+        <v>575247</v>
       </c>
       <c r="R63" t="n">
-        <v>7012646</v>
+        <v>7012737</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6804,12 +6730,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6824,22 +6750,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129701829</v>
+        <v>129678437</v>
       </c>
       <c r="B64" t="n">
-        <v>91628</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6847,37 +6773,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>575378</v>
+        <v>575201</v>
       </c>
       <c r="R64" t="n">
-        <v>7012599</v>
+        <v>7012827</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6901,12 +6832,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6921,60 +6852,65 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129702542</v>
+        <v>129678438</v>
       </c>
       <c r="B65" t="n">
-        <v>80230</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>575538</v>
+        <v>575264</v>
       </c>
       <c r="R65" t="n">
-        <v>7012552</v>
+        <v>7012697</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6998,12 +6934,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7018,22 +6954,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129702002</v>
+        <v>129678818</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7059,24 +6995,27 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>575427</v>
+        <v>575350</v>
       </c>
       <c r="R66" t="n">
-        <v>7012593</v>
+        <v>7012785</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7100,17 +7039,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7125,22 +7059,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129702401</v>
+        <v>129700719</v>
       </c>
       <c r="B67" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,34 +7082,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>575471</v>
+        <v>575458</v>
       </c>
       <c r="R67" t="n">
-        <v>7012565</v>
+        <v>7012663</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7208,6 +7147,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7234,10 +7178,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129701965</v>
+        <v>129701172</v>
       </c>
       <c r="B68" t="n">
-        <v>91624</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7245,34 +7189,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>575412</v>
+        <v>575342</v>
       </c>
       <c r="R68" t="n">
-        <v>7012614</v>
+        <v>7012553</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7305,6 +7254,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7331,45 +7285,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129702771</v>
+        <v>129701902</v>
       </c>
       <c r="B69" t="n">
-        <v>92346</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>575545</v>
+        <v>575412</v>
       </c>
       <c r="R69" t="n">
-        <v>7012515</v>
+        <v>7012629</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7402,6 +7361,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7428,45 +7392,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129702290</v>
+        <v>129702002</v>
       </c>
       <c r="B70" t="n">
-        <v>83048</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>575476</v>
+        <v>575427</v>
       </c>
       <c r="R70" t="n">
-        <v>7012589</v>
+        <v>7012593</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7499,6 +7468,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7525,10 +7499,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129702355</v>
+        <v>129702105</v>
       </c>
       <c r="B71" t="n">
-        <v>91624</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7536,34 +7510,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>575474</v>
+        <v>575427</v>
       </c>
       <c r="R71" t="n">
-        <v>7012588</v>
+        <v>7012592</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7596,6 +7575,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7622,10 +7606,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129712551</v>
+        <v>129702459</v>
       </c>
       <c r="B72" t="n">
-        <v>80194</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7633,37 +7617,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Erik-Elias bodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>575310</v>
+        <v>575495</v>
       </c>
       <c r="R72" t="n">
-        <v>7012647</v>
+        <v>7012552</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7687,12 +7676,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7707,22 +7701,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129700952</v>
+        <v>129702749</v>
       </c>
       <c r="B73" t="n">
-        <v>83065</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7730,34 +7724,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>575428</v>
+        <v>575545</v>
       </c>
       <c r="R73" t="n">
-        <v>7012641</v>
+        <v>7012515</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -7790,6 +7789,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7816,10 +7820,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129701072</v>
+        <v>129712548</v>
       </c>
       <c r="B74" t="n">
-        <v>79089</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7827,37 +7831,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>575348</v>
+        <v>575383</v>
       </c>
       <c r="R74" t="n">
-        <v>7012619</v>
+        <v>7012472</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7881,12 +7890,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7901,22 +7910,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129702579</v>
+        <v>129712549</v>
       </c>
       <c r="B75" t="n">
-        <v>91628</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7924,37 +7933,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+          <t>Erik-Elias bodarna, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>575529</v>
+        <v>575210</v>
       </c>
       <c r="R75" t="n">
-        <v>7012502</v>
+        <v>7012839</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7978,12 +7992,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7998,15 +8012,310 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129712557</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Erik-Elias bodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>575284</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7012519</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129700543</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Erik-Eliasbodarna, Erik-Eliasbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>575483</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7012735</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129702616</v>
+      </c>
+      <c r="B78" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Prästflobäcken, Prästflobäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>575529</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7012502</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48369-2025 artfynd.xlsx
+++ b/artfynd/A 48369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700955</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700982</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701965</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702355</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678414</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678415</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678416</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678417</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678418</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678419</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678420</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678421</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678422</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678423</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701024</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701829</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702579</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678440</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678441</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678442</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678443</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128580868</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700923</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700911</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702771</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701118</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128580870</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700674</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700728</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701072</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701251</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701504</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702401</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702707</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712558</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702290</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702652</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700952</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678444</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678445</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678446</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678447</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678448</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712551</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712552</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712553</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712554</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701129</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702542</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5535,6 +5785,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128580869</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5637,6 +5892,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678425</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5739,6 +5999,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678426</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5841,6 +6106,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678427</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5943,6 +6213,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678428</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6045,6 +6320,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678429</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6147,6 +6427,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678430</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6249,6 +6534,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678431</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6351,6 +6641,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678432</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6453,6 +6748,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678433</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6555,6 +6855,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678434</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6657,6 +6962,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678435</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6759,6 +7069,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678436</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6861,6 +7176,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678437</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6963,6 +7283,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678438</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7068,6 +7393,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129678818</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7175,6 +7505,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700719</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7282,6 +7617,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701172</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7389,6 +7729,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129701902</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7496,6 +7841,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702002</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7603,6 +7953,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702105</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7710,6 +8065,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702459</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7817,6 +8177,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702749</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7919,6 +8284,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712548</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8021,6 +8391,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712549</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8122,6 +8497,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712557</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8219,6 +8599,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129700543</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8316,8 +8701,92 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129702616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>